--- a/src/attributions/attributions_ig_traj_109.xlsx
+++ b/src/attributions/attributions_ig_traj_109.xlsx
@@ -1571,16 +1571,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02656434673178802</v>
+        <v>0.005508868505583513</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.01593118581404646</v>
+        <v>0.0002190167892079531</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1589,43 +1589,43 @@
         <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001928615805047359</v>
+        <v>4.576793305227101e-05</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04272205426305541</v>
+        <v>0.009505347686896867</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.03470881606789052</v>
+        <v>-0.002023698228884698</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.01451379162876084</v>
+        <v>-0.0006074073505012127</v>
       </c>
       <c r="R3" t="n">
         <v>-0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.05836862915600966</v>
+        <v>0.00755756767522292</v>
       </c>
       <c r="U3" t="n">
         <v>-0</v>
@@ -1634,52 +1634,52 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.01682863592876653</v>
+        <v>-0.004334123683044276</v>
       </c>
       <c r="X3" t="n">
         <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.04074139203771835</v>
+        <v>0.0001468796080945778</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.01295827112662216</v>
+        <v>-0.0004581955535700162</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.06967629053153632</v>
+        <v>-0.00380749679231315</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.001889306765643921</v>
+        <v>0.003145152704708462</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK3" t="n">
         <v>-0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0004835443591057922</v>
+        <v>0.01018886313378045</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
@@ -1688,16 +1688,16 @@
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.07884219603685289</v>
+        <v>0.004858850866474743</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.02458389304508113</v>
+        <v>8.671178424829981e-05</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
@@ -1706,7 +1706,7 @@
         <v>-0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.1515384625376861</v>
+        <v>0.02285662264049071</v>
       </c>
       <c r="AV3" t="n">
         <v>-0</v>
@@ -1715,7 +1715,7 @@
         <v>-0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0751863941531149</v>
+        <v>-0.001171040337044382</v>
       </c>
       <c r="AY3" t="n">
         <v>-0</v>
@@ -1724,7 +1724,7 @@
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.06786575272862137</v>
+        <v>-0.001846593941756171</v>
       </c>
       <c r="BB3" t="n">
         <v>-0</v>
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>-1.186115395690212e-11</v>
+        <v>-5.167072887906055e-13</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1742,16 +1742,16 @@
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.009853715773747745</v>
+        <v>0.0005469978202692947</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.02166579988568474</v>
+        <v>0.0001731035445817973</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.05024838736980161</v>
+        <v>0.001975379191994245</v>
       </c>
       <c r="BN3" t="n">
         <v>-0</v>
@@ -1769,16 +1769,16 @@
         <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.01306282348233104</v>
+        <v>0.003150443304898875</v>
       </c>
       <c r="BQ3" t="n">
         <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.01181155643469903</v>
+        <v>0.001200305283083086</v>
       </c>
       <c r="BT3" t="n">
         <v>-0</v>
@@ -1787,88 +1787,88 @@
         <v>-0</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.130541264522657</v>
+        <v>0.01702553060014964</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.003405906446649769</v>
+        <v>0.000214990066359604</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.01406443849159864</v>
+        <v>-0.00449484791966951</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.01612279617319321</v>
+        <v>-0.006279022826856801</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG3" t="n">
         <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.01055693787016951</v>
+        <v>-0.002556282837266034</v>
       </c>
       <c r="CI3" t="n">
         <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.01381770477283021</v>
+        <v>0.0004475356687265247</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
         <v>0</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.02646254904162565</v>
+        <v>-0.01066338244205369</v>
       </c>
       <c r="CO3" t="n">
         <v>-0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.08303259315987366</v>
+        <v>0.005236183416441119</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.006267445703342499</v>
+        <v>0.00209488991191445</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
         <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.002821276895101323</v>
+        <v>-0.006289456015757275</v>
       </c>
       <c r="CX3" t="n">
         <v>0</v>
@@ -1877,43 +1877,43 @@
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.008207037134693094</v>
+        <v>-0.001134491316159161</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.0107672737430197</v>
+        <v>0.0001614780691905378</v>
       </c>
       <c r="DD3" t="n">
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.1277225821002947</v>
+        <v>-0.006150690249007711</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.0142486614268827</v>
+        <v>-0.005332576956643896</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
         <v>-0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0.03637967677501492</v>
+        <v>-0.0001953815123298123</v>
       </c>
       <c r="DM3" t="n">
         <v>-0</v>
@@ -1922,34 +1922,34 @@
         <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.01770761831912057</v>
+        <v>-0.009154970741633366</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.002909730384214921</v>
+        <v>0.0002731147018837768</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
         <v>0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.004213746881595547</v>
+        <v>0.004379688121157436</v>
       </c>
       <c r="DV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.07260960990998191</v>
+        <v>0.005723469654770296</v>
       </c>
       <c r="DY3" t="n">
         <v>-0</v>
@@ -1958,34 +1958,34 @@
         <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.03522539812648993</v>
+        <v>0.004975490251019367</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.02418108753209067</v>
+        <v>-0.001199585688109578</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.0340579701548345</v>
+        <v>-0.001361177892236985</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0002312462701287223</v>
+        <v>-0.005339230000826462</v>
       </c>
       <c r="EK3" t="n">
         <v>-0</v>
@@ -1994,7 +1994,7 @@
         <v>-0</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.04954073988128781</v>
+        <v>-0.001229481159508579</v>
       </c>
       <c r="EN3" t="n">
         <v>0</v>
@@ -2003,34 +2003,34 @@
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0.01645116029274218</v>
+        <v>-0.001725655994297373</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER3" t="n">
         <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.03938612634159396</v>
+        <v>-0.001885319259424121</v>
       </c>
       <c r="ET3" t="n">
         <v>-0</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.06572295222670688</v>
+        <v>-0.001421578338680959</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.01778250489667954</v>
+        <v>-0.007862840896295367</v>
       </c>
       <c r="EZ3" t="n">
         <v>-0</v>
@@ -2039,7 +2039,7 @@
         <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.003610801833014698</v>
+        <v>-0.003512687202605231</v>
       </c>
       <c r="FC3" t="n">
         <v>-0</v>
@@ -2048,43 +2048,43 @@
         <v>-0</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.006770986225581659</v>
+        <v>0.0003315953539673046</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.0123261487334901</v>
+        <v>-0.0004565294425411786</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.04277087610715016</v>
+        <v>0.002994650467309309</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN3" t="n">
-        <v>-0.04793258355486135</v>
+        <v>-0.003823778923137184</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP3" t="n">
         <v>-0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.00248725968512938</v>
+        <v>-0.001017752977095774</v>
       </c>
       <c r="FR3" t="n">
         <v>-0</v>
@@ -2093,7 +2093,7 @@
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.004101840771886286</v>
+        <v>0.0006426030989894392</v>
       </c>
       <c r="FU3" t="n">
         <v>-0</v>
@@ -2102,34 +2102,34 @@
         <v>0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0.03398400450480307</v>
+        <v>0.005349632705230266</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.01691077744918437</v>
+        <v>-0.005302567047060539</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
         <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0.0319706820253767</v>
+        <v>-0.00189093982696886</v>
       </c>
       <c r="GG3" t="n">
         <v>0</v>
@@ -2137,10 +2137,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.002136760794463802</v>
+        <v>-0.03224390549872354</v>
       </c>
       <c r="B4" t="n">
-        <v>0.06320938954935283</v>
+        <v>0.04598242982726048</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2149,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04863725543772884</v>
+        <v>0.02233940201598358</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2164,10 +2164,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.008525911429434664</v>
+        <v>-0.02910289940618375</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06966490161336487</v>
+        <v>0.08583744529502028</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03671232445621048</v>
+        <v>0.0284078784923695</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -2191,25 +2191,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04115469671414898</v>
+        <v>0.01052639392302103</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1088874103333396</v>
+        <v>0.01607391062819321</v>
       </c>
       <c r="U4" t="n">
         <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1166744514892477</v>
+        <v>0.005711775283655819</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" t="n">
         <v>-0</v>
@@ -2218,25 +2218,25 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.006013757532810109</v>
+        <v>-0.01142621930665273</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.03185608605705548</v>
+        <v>-0.002808447109775839</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.002791855370268356</v>
+        <v>-0.0182419084164994</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
@@ -2245,10 +2245,10 @@
         <v>-0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.04483356840424626</v>
+        <v>-0.01608884183177159</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.02917765378967275</v>
+        <v>0.06164448093853463</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,25 +2257,25 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.05195176273776796</v>
+        <v>0.04425117429209616</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.122540674682214</v>
+        <v>-0.02664101362082801</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.1790891992415553</v>
+        <v>0.1261923678047104</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
@@ -2284,25 +2284,25 @@
         <v>-0</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.4047903969044649</v>
+        <v>0.01002634000702831</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>-0.007877339027816165</v>
+        <v>-0.01124038647493152</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.003126070239171119</v>
+        <v>0.001173764885922213</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -2311,7 +2311,7 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-4.253506479632123e-11</v>
+        <v>-1.433365274078688e-11</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
@@ -2326,25 +2326,25 @@
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0.00205081504188688</v>
+        <v>0.004022608154499839</v>
       </c>
       <c r="BM4" t="n">
-        <v>-0.01180190895650786</v>
+        <v>0.006331359158763605</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.03674723410925121</v>
+        <v>0.02255530718921927</v>
       </c>
       <c r="BQ4" t="n">
         <v>-0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2353,49 +2353,49 @@
         <v>-0</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.06414687071111648</v>
+        <v>0.001522331634688522</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1148494980049262</v>
+        <v>0.1025611284465476</v>
       </c>
       <c r="BW4" t="n">
         <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.1708361172531732</v>
+        <v>0.04726363208768822</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
       </c>
       <c r="CD4" t="n">
-        <v>-0.005639103876406129</v>
+        <v>0.03278325740078016</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.04894081274988328</v>
+        <v>-0.05210055111987161</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.05101685621564688</v>
+        <v>-0.03870861056442844</v>
       </c>
       <c r="CI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ4" t="n">
         <v>-0</v>
@@ -2407,19 +2407,19 @@
         <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0.06586810813977589</v>
+        <v>0.0172403467194677</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0247519637133949</v>
+        <v>-0.08817233337771913</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.1734790849853298</v>
+        <v>0.01269407822975771</v>
       </c>
       <c r="CR4" t="n">
         <v>-0</v>
@@ -2428,28 +2428,28 @@
         <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>-0.01488442131354483</v>
+        <v>0.02229230018671522</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.05688673299032307</v>
+        <v>-0.0514440384843008</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.04836909312227668</v>
+        <v>-0.04810758754969634</v>
       </c>
       <c r="DA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB4" t="n">
         <v>0</v>
@@ -2461,19 +2461,19 @@
         <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.01105009839720026</v>
+        <v>0.01614406536259669</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.1360827038227628</v>
+        <v>-0.07226636581062559</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
         <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.05783225637167023</v>
+        <v>-0.07585026894930666</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
@@ -2482,31 +2482,31 @@
         <v>-0</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM4" t="n">
         <v>-0</v>
       </c>
       <c r="DN4" t="n">
-        <v>-0.03109965118252964</v>
+        <v>0.003327350681708384</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.06808551257646567</v>
+        <v>-0.02507658322768679</v>
       </c>
       <c r="DP4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.01795114068868946</v>
+        <v>0.008623776243924379</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>-0</v>
@@ -2515,64 +2515,64 @@
         <v>-0</v>
       </c>
       <c r="DW4" t="n">
-        <v>-0.02653210283943028</v>
+        <v>0.05398674971263164</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.07786648438493921</v>
+        <v>0.09145729337963231</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
         <v>0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.03076145475237695</v>
+        <v>-0.01140126781060571</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
         <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0.04211999078339419</v>
+        <v>0.006784618496050727</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.04197033892563651</v>
+        <v>-0.003107854025730179</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.08691440055084733</v>
+        <v>-0.0605071631595983</v>
       </c>
       <c r="EK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL4" t="n">
         <v>-0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
         <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>-0.009185613739613963</v>
+        <v>0.02198815094948434</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.07004842138079879</v>
+        <v>-0.01586860275353678</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
@@ -2581,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.08975139169991908</v>
+        <v>-0.05407415802719559</v>
       </c>
       <c r="ET4" t="n">
         <v>-0</v>
@@ -2596,10 +2596,10 @@
         <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0.01772957151748001</v>
+        <v>0.03280234483133212</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.07032650660974543</v>
+        <v>-0.05890643448547762</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.06762748431680954</v>
+        <v>-0.05964298608211195</v>
       </c>
       <c r="FC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD4" t="n">
         <v>-0</v>
@@ -2623,37 +2623,37 @@
         <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.03371024912258422</v>
+        <v>-0.0142249700592702</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.009363778553548533</v>
+        <v>-0.01295713774534843</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.02249189835404659</v>
+        <v>-0.04659173135071591</v>
       </c>
       <c r="FL4" t="n">
         <v>0</v>
       </c>
       <c r="FM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO4" t="n">
         <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.01717525711698997</v>
+        <v>0.06201730221793361</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.003675894050368758</v>
+        <v>-0.001646284284549831</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
@@ -2662,7 +2662,7 @@
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.01207609047033657</v>
+        <v>0.01198366433916622</v>
       </c>
       <c r="FU4" t="n">
         <v>-0</v>
@@ -2671,16 +2671,16 @@
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0.02311234820713727</v>
+        <v>0.01501830610196653</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.05753296487314905</v>
+        <v>-0.04913201603806167</v>
       </c>
       <c r="GA4" t="n">
         <v>-0</v>
@@ -2689,10 +2689,10 @@
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
         <v>0</v>
@@ -2701,7 +2701,7 @@
         <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,103 +2709,103 @@
         <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.06465138853821394</v>
+        <v>0.001354325645076309</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.008872603333480772</v>
+        <v>-0.0002179382034854954</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.04015265442866398</v>
+        <v>-0.0003612797697032376</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05749638425677297</v>
+        <v>0.002612589667526367</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01429865570658291</v>
+        <v>-9.917762148400575e-05</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.03518598792540947</v>
+        <v>-0.0007837803425275306</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5" t="n">
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.08394952379298284</v>
+        <v>2.106205577141619e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.08258200082313868</v>
+        <v>-0.001196006088709078</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.01476137011159206</v>
+        <v>-4.73883858308279e-05</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB5" t="n">
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.07141292955010196</v>
+        <v>-0.0001318660246295226</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.01211239799348523</v>
+        <v>-0.001736845871050792</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001846652193553068</v>
+        <v>-0.00031579451973865</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
@@ -2814,28 +2814,28 @@
         <v>-0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.04632860306783729</v>
+        <v>0.002286712586682046</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.02388152880416084</v>
+        <v>0.0003979386878664077</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.05791328428264075</v>
+        <v>-0.0004027664493962577</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
@@ -2844,49 +2844,49 @@
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.196746434100476</v>
+        <v>0.007916070107388087</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1227895199426897</v>
+        <v>0.0005526317110448216</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.06951254304867259</v>
+        <v>-0.0009956436587939183</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0003616555958228447</v>
+        <v>-0.0003764951950485766</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF5" t="n">
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.008755902656196827</v>
+        <v>-0.0001979464146051305</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.003231826725814426</v>
+        <v>4.521682765487798e-05</v>
       </c>
       <c r="BJ5" t="n">
         <v>0</v>
@@ -2895,10 +2895,10 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.0116280526132181</v>
+        <v>0.0006497377253504315</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
@@ -2907,13 +2907,13 @@
         <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.03355433273473499</v>
+        <v>0.001544944975002272</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.02644438112710741</v>
+        <v>-7.296905309754468e-05</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,34 +2925,34 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.08305720832203665</v>
+        <v>0.004639245575160495</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.07156005285122845</v>
+        <v>0.0003693346879801363</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.02777500130347296</v>
+        <v>2.525161009792616e-05</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.0476634630971231</v>
+        <v>-0.001267421076989617</v>
       </c>
       <c r="CF5" t="n">
         <v>0</v>
@@ -2961,13 +2961,13 @@
         <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.002457046662722426</v>
+        <v>-0.0001031615579094515</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.02255228040110745</v>
+        <v>0.0001440768692394427</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
@@ -2976,25 +2976,25 @@
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.05530678099767569</v>
+        <v>-0.002907570377349095</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.06173286399417392</v>
+        <v>-0.0003785078840115239</v>
       </c>
       <c r="CR5" t="n">
         <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.02257985640781444</v>
+        <v>-0.00127550594316506</v>
       </c>
       <c r="CT5" t="n">
         <v>-0</v>
@@ -3003,10 +3003,10 @@
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.05031695768643304</v>
+        <v>-0.001417293927296984</v>
       </c>
       <c r="CX5" t="n">
         <v>-0</v>
@@ -3015,70 +3015,70 @@
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.001751085754587383</v>
+        <v>-0.0003420833261171647</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.03338934756871535</v>
+        <v>0.0005192640310153481</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD5" t="n">
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.09802692405754559</v>
+        <v>-0.0004094536525891241</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.07621349577970443</v>
+        <v>-0.001287886363775995</v>
       </c>
       <c r="DJ5" t="n">
         <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.003768311273928559</v>
+        <v>-0.001320107472887702</v>
       </c>
       <c r="DL5" t="n">
         <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.01426519792855243</v>
+        <v>-0.0009442021258312634</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.02008079606987979</v>
+        <v>0.0002425409428563404</v>
       </c>
       <c r="DS5" t="n">
         <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.03105823041515706</v>
+        <v>0.001075520684145114</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
@@ -3087,22 +3087,22 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.05767855230341743</v>
+        <v>0.001222673406798967</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.00644747976364275</v>
+        <v>-0.0004191422247541627</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.002384799441273657</v>
+        <v>0.0004184991482505014</v>
       </c>
       <c r="ED5" t="n">
         <v>0</v>
@@ -3111,28 +3111,28 @@
         <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.008373426433711726</v>
+        <v>-0.001103981557069689</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
         <v>-0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.001974834054483543</v>
+        <v>-0.001060207268453302</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.04698760768568452</v>
+        <v>-0.0003222009420626221</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
@@ -3141,115 +3141,115 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.04542771981146902</v>
+        <v>-0.000523778995123939</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
         <v>-0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.006834810361751678</v>
+        <v>-0.0005785913711789689</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.03688582882540516</v>
+        <v>0.0007156060011999779</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW5" t="n">
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.04783350083841916</v>
+        <v>-0.001649574350333806</v>
       </c>
       <c r="EZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.01493318541161768</v>
+        <v>-0.0009042490210884474</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.03058688364091862</v>
+        <v>0.0004334687201620635</v>
       </c>
       <c r="FE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.02605659520474942</v>
+        <v>7.664040241573983e-05</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.0287996523911154</v>
+        <v>-0.0001499850005714565</v>
       </c>
       <c r="FL5" t="n">
         <v>0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.01527201111552786</v>
+        <v>0.0003201783829468074</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.006914679325213004</v>
+        <v>7.265805730835973e-05</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.002185826435294436</v>
+        <v>-1.15334762858727e-05</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.05019586797226934</v>
+        <v>0.001148396489420706</v>
       </c>
       <c r="FW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX5" t="n">
         <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.01474680022051014</v>
+        <v>-0.001451430993987432</v>
       </c>
       <c r="GA5" t="n">
         <v>-0</v>
@@ -3261,10 +3261,10 @@
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
-        <v>-0.001320387974890898</v>
+        <v>0.000899150445580826</v>
       </c>
       <c r="GF5" t="n">
         <v>-0</v>
@@ -3278,115 +3278,115 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.07676007859944481</v>
+        <v>0.3753450773629454</v>
       </c>
       <c r="C6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01734379811207104</v>
+        <v>-0.1567029052096607</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
         <v>-0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.05579299572640013</v>
+        <v>-0.1060124730925686</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0346402687791986</v>
+        <v>0.5441097526051779</v>
       </c>
       <c r="L6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.01087935797680939</v>
+        <v>-0.1170505462692208</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.07721331508972973</v>
+        <v>-0.102525685496639</v>
       </c>
       <c r="S6" t="n">
         <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03288205698990535</v>
+        <v>0.07657215036038101</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03715423599560197</v>
+        <v>-0.3179398800677883</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.01865086893948072</v>
+        <v>-0.2527949489369182</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.06184965842069695</v>
+        <v>0.072287084947481</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.006340468570569226</v>
+        <v>-0.2260446848417945</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.02637552557701811</v>
+        <v>-0.09048555036018159</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.03297119658272682</v>
+        <v>0.3301769951377542</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -3395,34 +3395,34 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.02041222618414162</v>
+        <v>0.185145307235263</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0242470235317048</v>
+        <v>-0.1215690645510796</v>
       </c>
       <c r="AT6" t="n">
         <v>-0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.2917854836955738</v>
+        <v>1.170916658558653</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.208548618119431</v>
+        <v>-0.02798465753604271</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
@@ -3434,22 +3434,22 @@
         <v>-0</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.05722287050543934</v>
+        <v>0.08213047095943236</v>
       </c>
       <c r="BC6" t="n">
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.008490534495219965</v>
+        <v>-0.04527075727825633</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.008975936559039633</v>
+        <v>-0.06292212710611329</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
@@ -3461,148 +3461,148 @@
         <v>0</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.009777222510315932</v>
+        <v>-0.01485395156639966</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.002611576976484966</v>
+        <v>0.02359314701721643</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.06239169174696133</v>
+        <v>0.1290567121123963</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.01956317229621448</v>
+        <v>0.1486508526538972</v>
       </c>
       <c r="BU6" t="n">
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.1196816571242564</v>
+        <v>0.7531654590575481</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.06507361744749179</v>
+        <v>-0.204565453844064</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.009651927384021545</v>
+        <v>-0.2694870979002017</v>
       </c>
       <c r="CD6" t="n">
         <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.03523352313946833</v>
+        <v>-0.4012184893697973</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
         <v>0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.01079404723635926</v>
+        <v>0.09422711516386961</v>
       </c>
       <c r="CI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.05569644524917984</v>
+        <v>0.1283974782488098</v>
       </c>
       <c r="CM6" t="n">
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.06867135273660441</v>
+        <v>-0.6288540381337823</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.1118344436023267</v>
+        <v>0.2034169831975039</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
         <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.00112503013938666</v>
+        <v>0.09335833314918363</v>
       </c>
       <c r="CV6" t="n">
         <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.03395866601227931</v>
+        <v>-0.3848160191855816</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.009412261450325962</v>
+        <v>0.06708854704959505</v>
       </c>
       <c r="DA6" t="n">
         <v>0</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.04757876155874516</v>
+        <v>0.1676787605893773</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.1212120952892918</v>
+        <v>-0.1700381947359416</v>
       </c>
       <c r="DG6" t="n">
         <v>-0</v>
@@ -3611,37 +3611,37 @@
         <v>-0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.05003706405820744</v>
+        <v>0.1172528511329942</v>
       </c>
       <c r="DJ6" t="n">
         <v>-0</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL6" t="n">
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0.04866477268923614</v>
+        <v>-0.2449605209382475</v>
       </c>
       <c r="DN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.02458072896715062</v>
+        <v>-0.2259000728842014</v>
       </c>
       <c r="DP6" t="n">
         <v>0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.002018665357792992</v>
+        <v>0.02021608131019708</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT6" t="n">
         <v>0</v>
@@ -3650,40 +3650,40 @@
         <v>-0</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.00940813408909256</v>
+        <v>0.01096047565940856</v>
       </c>
       <c r="DW6" t="n">
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.0423016355217649</v>
+        <v>0.222546292820008</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
         <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.006192037904076834</v>
+        <v>-0.08733995187250471</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.004358439988377122</v>
+        <v>0.1803702625439507</v>
       </c>
       <c r="EF6" t="n">
         <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.004347880156865189</v>
+        <v>-0.2301992339205212</v>
       </c>
       <c r="EH6" t="n">
         <v>0</v>
@@ -3692,37 +3692,37 @@
         <v>0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.01359267674122726</v>
+        <v>-0.06194147200962984</v>
       </c>
       <c r="EK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.06636626394904335</v>
+        <v>0.05657364923028487</v>
       </c>
       <c r="EO6" t="n">
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.04948577350883685</v>
+        <v>-0.1879052677065986</v>
       </c>
       <c r="EQ6" t="n">
         <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.0003879001183080452</v>
+        <v>0.1055101194232237</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
         <v>-0</v>
@@ -3731,40 +3731,40 @@
         <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.01987303948371004</v>
+        <v>0.1392401118697435</v>
       </c>
       <c r="EX6" t="n">
         <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.04346599096447747</v>
+        <v>-0.4475167914452595</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.01486862939168749</v>
+        <v>0.05366092761618014</v>
       </c>
       <c r="FC6" t="n">
         <v>-0</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.03754195779908069</v>
+        <v>0.147245055186596</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.06981798327221392</v>
+        <v>-0.1806524042146679</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
@@ -3773,55 +3773,55 @@
         <v>0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.02865673147543807</v>
+        <v>-0.05824330069243067</v>
       </c>
       <c r="FL6" t="n">
         <v>0</v>
       </c>
       <c r="FM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN6" t="n">
         <v>0</v>
       </c>
       <c r="FO6" t="n">
-        <v>-0.03833273620942305</v>
+        <v>-0.115173343911928</v>
       </c>
       <c r="FP6" t="n">
         <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.003492717135003391</v>
+        <v>-0.03694471959925368</v>
       </c>
       <c r="FR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS6" t="n">
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.01505464128325796</v>
+        <v>0.01404352887448424</v>
       </c>
       <c r="FU6" t="n">
         <v>-0</v>
       </c>
       <c r="FV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
-        <v>-0.003948536725794574</v>
+        <v>0.05972827719934005</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.06385097138572778</v>
+        <v>-0.2287302482368401</v>
       </c>
       <c r="GA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
@@ -3830,16 +3830,16 @@
         <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0.004476267790892425</v>
+        <v>0.1035178015901476</v>
       </c>
     </row>
     <row r="7">
@@ -4413,25 +4413,25 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2340966807088092</v>
+        <v>0.08924265167927893</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2154113655580816</v>
+        <v>-0.03668122107257622</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09924319133449046</v>
+        <v>-0.02640679091662923</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
@@ -4443,22 +4443,22 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2249777552310245</v>
+        <v>0.1252798491911924</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1655536903616837</v>
+        <v>-0.03157590846858616</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01864369855613501</v>
+        <v>-0.02833547547235617</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -4470,160 +4470,160 @@
         <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.06411796863333109</v>
+        <v>0.02576031139877554</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.02313184138686851</v>
+        <v>0.01889134877203242</v>
       </c>
       <c r="V8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1094013856730152</v>
+        <v>0.0267280845504421</v>
       </c>
       <c r="X8" t="n">
         <v>-0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.1266294714621056</v>
+        <v>0.01141210977312668</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.005333845676602635</v>
+        <v>-0.02754971986477718</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1340446333444399</v>
+        <v>-0.03018997439034705</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
         <v>-0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.1329584366484133</v>
+        <v>0.09892940165630347</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0.1173599455619566</v>
+        <v>-0.0143457116537351</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0325208576428536</v>
+        <v>0.06390823791165767</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT8" t="n">
         <v>-0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.2246751509843058</v>
+        <v>0.1976217516285271</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.2489482196300369</v>
+        <v>0.03448876468281691</v>
       </c>
       <c r="AW8" t="n">
         <v>-0</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.1324485527124863</v>
+        <v>-0.01971798669224962</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.07017704635297196</v>
+        <v>-0.01561666664435389</v>
       </c>
       <c r="BE8" t="n">
-        <v>-0.07703387587011619</v>
+        <v>-0.04379262916703944</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.01999052363935399</v>
+        <v>-0.02777084268268738</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI8" t="n">
         <v>-0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.02241230462944487</v>
+        <v>-0.008229969075643589</v>
       </c>
       <c r="BN8" t="n">
-        <v>-0.03862963139088484</v>
+        <v>-0.0008024688027530387</v>
       </c>
       <c r="BO8" t="n">
         <v>0</v>
       </c>
       <c r="BP8" t="n">
-        <v>-6.098692632623038e-05</v>
+        <v>0.00911775282909847</v>
       </c>
       <c r="BQ8" t="n">
         <v>-0</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT8" t="n">
         <v>-0</v>
@@ -4632,22 +4632,22 @@
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.09092048459267579</v>
+        <v>0.1318365897879862</v>
       </c>
       <c r="BW8" t="n">
-        <v>-0.2192069026321691</v>
+        <v>0.01621984263139032</v>
       </c>
       <c r="BX8" t="n">
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.126176560323092</v>
+        <v>0.02387043471025579</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB8" t="n">
         <v>0</v>
@@ -4656,28 +4656,28 @@
         <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.1059470408091621</v>
+        <v>-0.08650608538443885</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.03891313639861396</v>
+        <v>0.02266635866599327</v>
       </c>
       <c r="CG8" t="n">
         <v>0</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.02730598071202895</v>
+        <v>0.008134102205694311</v>
       </c>
       <c r="CI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ8" t="n">
         <v>-0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL8" t="n">
         <v>-0</v>
@@ -4686,19 +4686,19 @@
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.01143256486527358</v>
+        <v>-0.1182896585711094</v>
       </c>
       <c r="CO8" t="n">
-        <v>-0.05430182767164252</v>
+        <v>0.01056550897639461</v>
       </c>
       <c r="CP8" t="n">
         <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.1153964134030319</v>
+        <v>0.05664866833105915</v>
       </c>
       <c r="CR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS8" t="n">
         <v>-0</v>
@@ -4710,19 +4710,19 @@
         <v>0</v>
       </c>
       <c r="CV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.09005364839171111</v>
+        <v>-0.08245281370803886</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.03204009720688458</v>
+        <v>0.02051441720148844</v>
       </c>
       <c r="CY8" t="n">
         <v>-0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.0483146639152198</v>
+        <v>0.0008290681736838129</v>
       </c>
       <c r="DA8" t="n">
         <v>0</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="DC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD8" t="n">
         <v>0</v>
@@ -4740,127 +4740,127 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.08865438398354297</v>
+        <v>-0.0346941302755506</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.003699740111618241</v>
+        <v>0.03236778143344828</v>
       </c>
       <c r="DH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0.09908910130614727</v>
+        <v>-0.008184087151771248</v>
       </c>
       <c r="DJ8" t="n">
         <v>-0</v>
       </c>
       <c r="DK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.04517185529370563</v>
+        <v>-0.03722367243767233</v>
       </c>
       <c r="DP8" t="n">
-        <v>-0.0302922090738084</v>
+        <v>-0.01932802509472318</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.01879581517643688</v>
+        <v>0.01091710292961957</v>
       </c>
       <c r="DS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.1119916559893057</v>
+        <v>0.07902738480723831</v>
       </c>
       <c r="DY8" t="n">
-        <v>-0.004635761624410742</v>
+        <v>0.02319909576570506</v>
       </c>
       <c r="DZ8" t="n">
         <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.04764680428471419</v>
+        <v>-0.0331399763162834</v>
       </c>
       <c r="EB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
         <v>-0</v>
       </c>
       <c r="EF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.02800257579881679</v>
+        <v>-0.05372489511514839</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.04248269238530242</v>
+        <v>-0.002098444591860457</v>
       </c>
       <c r="EI8" t="n">
         <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.03436028793099136</v>
+        <v>0.001029872857668706</v>
       </c>
       <c r="EK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN8" t="n">
         <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.08038979769438731</v>
+        <v>-0.05710684845535878</v>
       </c>
       <c r="EQ8" t="n">
-        <v>-0.01880462977183438</v>
+        <v>-0.003938304390454454</v>
       </c>
       <c r="ER8" t="n">
         <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.02484429724868246</v>
+        <v>0.009808529266190087</v>
       </c>
       <c r="ET8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU8" t="n">
         <v>-0</v>
@@ -4872,19 +4872,19 @@
         <v>-0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.1066792484810939</v>
+        <v>-0.09399283776169998</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.03162363043443308</v>
+        <v>0.02055439976805449</v>
       </c>
       <c r="FA8" t="n">
         <v>0</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.03611371958490356</v>
+        <v>0.004047911527346233</v>
       </c>
       <c r="FC8" t="n">
         <v>-0</v>
@@ -4893,28 +4893,28 @@
         <v>-0</v>
       </c>
       <c r="FE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF8" t="n">
         <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.02737173580088669</v>
+        <v>0.0006551587335141327</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0.05973200873057419</v>
+        <v>-0.05690101652400423</v>
       </c>
       <c r="FJ8" t="n">
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.137727805637721</v>
+        <v>-0.05605343660340779</v>
       </c>
       <c r="FL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM8" t="n">
         <v>0</v>
@@ -4923,22 +4923,22 @@
         <v>-0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
         <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.0008872533456813478</v>
+        <v>-0.0002422247579380162</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.04471550429511153</v>
+        <v>0.004419023250198523</v>
       </c>
       <c r="FS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.02156358046595722</v>
+        <v>0.003612696588820849</v>
       </c>
       <c r="FU8" t="n">
         <v>-0</v>
@@ -4950,31 +4950,31 @@
         <v>-0</v>
       </c>
       <c r="FX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.07656818832319674</v>
+        <v>-0.06424598350664225</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0.06820845176041138</v>
+        <v>-0.03016414524145234</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC8" t="n">
         <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
         <v>0</v>
@@ -4982,10 +4982,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1778886720751335</v>
+        <v>1.197365355671436</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -4994,25 +4994,25 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.01280536736169042</v>
+        <v>-0.4666438681646258</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08670415349764159</v>
+        <v>-0.1331019900155638</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1397398863827395</v>
+        <v>1.605017000134339</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -5021,79 +5021,79 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.04663556649451849</v>
+        <v>-0.6037297910590089</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.08512949487424212</v>
+        <v>-0.1030979949637824</v>
       </c>
       <c r="S9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.07264661550386825</v>
+        <v>0.166477185625848</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.06744373179219336</v>
+        <v>-0.1947760706508349</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z9" t="n">
         <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.04316213245347071</v>
+        <v>-0.3675030095690307</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.07680810216308941</v>
+        <v>0.1371405791169672</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01983735364755818</v>
+        <v>-0.1595148736665555</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.005381564194212126</v>
+        <v>0.1190419111930241</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.06803809677246221</v>
+        <v>0.9196495380638161</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
@@ -5102,52 +5102,52 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.01012594713154203</v>
+        <v>0.452503378337297</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0.0590617996857869</v>
+        <v>-0.04368207660126987</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.3101803889750839</v>
+        <v>2.342486077226077</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1676005363128526</v>
+        <v>-0.5065278261664886</v>
       </c>
       <c r="AY9" t="n">
         <v>-0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>-0.02440972472259947</v>
+        <v>0.02800964982939386</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.008247463417357498</v>
+        <v>-0.1462380578536531</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -5156,52 +5156,52 @@
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.06098438954428136</v>
+        <v>-0.2435269249496101</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
-        <v>-0.069434775873122</v>
+        <v>-0.1026731086309063</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>-0.006764670013387033</v>
+        <v>-0.002508720479665111</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.06212018696730483</v>
+        <v>0.2380878226343246</v>
       </c>
       <c r="BQ9" t="n">
         <v>-0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0.004235349301375518</v>
+        <v>0.1247170203389953</v>
       </c>
       <c r="BU9" t="n">
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.1770318083904806</v>
+        <v>1.487506643849603</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
@@ -5210,25 +5210,25 @@
         <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.1164321624125968</v>
+        <v>-0.3425852049476904</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0.0143929654617496</v>
+        <v>-0.2471448681324605</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.06330553512880761</v>
+        <v>-0.9486340119099808</v>
       </c>
       <c r="CF9" t="n">
         <v>-0</v>
@@ -5237,25 +5237,25 @@
         <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.01206860469580327</v>
+        <v>0.1274671458297957</v>
       </c>
       <c r="CI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.04333127738340158</v>
+        <v>0.07786119311223025</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.05824750089026644</v>
+        <v>-1.285077912627075</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
@@ -5264,10 +5264,10 @@
         <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.09138566923926789</v>
+        <v>0.2939892608246747</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
@@ -5276,22 +5276,22 @@
         <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>-0.004064317398683574</v>
+        <v>-0.01619383585162506</v>
       </c>
       <c r="CV9" t="n">
         <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.06309221855286656</v>
+        <v>-0.8921861955467794</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
         <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.01337488204369053</v>
+        <v>0.1110337059849143</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
@@ -5300,25 +5300,25 @@
         <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0452438730154018</v>
+        <v>0.1730714085041537</v>
       </c>
       <c r="DE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.09309245519420903</v>
+        <v>-0.1183560664424621</v>
       </c>
       <c r="DG9" t="n">
         <v>-0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.09335680771367115</v>
+        <v>-0.2500711489379323</v>
       </c>
       <c r="DJ9" t="n">
         <v>-0</v>
@@ -5327,43 +5327,43 @@
         <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.009138307550907766</v>
+        <v>-0.2466732776160344</v>
       </c>
       <c r="DN9" t="n">
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.01997607192881714</v>
+        <v>-0.4801323964683187</v>
       </c>
       <c r="DP9" t="n">
         <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.02421804642518163</v>
+        <v>-0.04151786463124045</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0.02688847606556273</v>
+        <v>-0.2403520979881973</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.05016001691253999</v>
+        <v>0.5733916592546139</v>
       </c>
       <c r="DY9" t="n">
         <v>-0</v>
@@ -5372,34 +5372,34 @@
         <v>-0</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.02529398772593068</v>
+        <v>-0.111560894482153</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.005661839598238611</v>
+        <v>0.1884518759879682</v>
       </c>
       <c r="EF9" t="n">
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.007110465772220738</v>
+        <v>-0.5494276360029707</v>
       </c>
       <c r="EH9" t="n">
         <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.002074395931151716</v>
+        <v>0.05571127376852086</v>
       </c>
       <c r="EK9" t="n">
         <v>-0</v>
@@ -5411,40 +5411,40 @@
         <v>-0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.06351283902944735</v>
+        <v>0.0123457560887269</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.07127126840329198</v>
+        <v>-0.4318611517189581</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.01939009172408909</v>
+        <v>0.1456795831617382</v>
       </c>
       <c r="ET9" t="n">
         <v>-0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0.04060224867583302</v>
+        <v>0.1464057444710317</v>
       </c>
       <c r="EX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.07625053912222855</v>
+        <v>-1.023825637708287</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
@@ -5453,82 +5453,82 @@
         <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.0257965912338757</v>
+        <v>0.07562764465839782</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.0383155188896189</v>
+        <v>0.1794547286258128</v>
       </c>
       <c r="FG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.05669985997946938</v>
+        <v>-0.4207233968292801</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.01398411413828483</v>
+        <v>-0.1001887766226093</v>
       </c>
       <c r="FL9" t="n">
         <v>0</v>
       </c>
       <c r="FM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.01748841845415235</v>
+        <v>0.5049793038644917</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.001496675379679626</v>
+        <v>-0.02104885261042194</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.0002205556751915835</v>
+        <v>0.005786797009422362</v>
       </c>
       <c r="FU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
         <v>-0</v>
       </c>
       <c r="FX9" t="n">
-        <v>-0.001903787237740012</v>
+        <v>-0.4335151197280002</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.06929384846202273</v>
+        <v>-0.501907578344422</v>
       </c>
       <c r="GA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB9" t="n">
         <v>-0</v>
@@ -5537,33 +5537,33 @@
         <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.0008779398902944745</v>
+        <v>0.2329672412588237</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.006874225494273859</v>
+        <v>-0.01544516229832262</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0674828135999237</v>
+        <v>0.02615338351275125</v>
       </c>
       <c r="C10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04667006441927866</v>
+        <v>0.001542837961333111</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5572,16 +5572,16 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.009311695300137868</v>
+        <v>-0.01373356773964439</v>
       </c>
       <c r="K10" t="n">
-        <v>0.07313322199684957</v>
+        <v>0.04297476811731189</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -5590,10 +5590,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01595958824280003</v>
+        <v>-0.002256952875158524</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -5605,64 +5605,64 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01967004193545815</v>
+        <v>0.008463387501109016</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0783024120211375</v>
+        <v>0.01214523372935334</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.08641864122451155</v>
+        <v>0.01120169324706957</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.002139828931554476</v>
+        <v>-0.003982109085542973</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.06906278536073204</v>
+        <v>0.004562197885761511</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.01002621962498735</v>
+        <v>-0.007349744147795577</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.01995819102689664</v>
+        <v>-0.003806897822888304</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.03230186120598363</v>
+        <v>0.01656677411070858</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
@@ -5671,25 +5671,25 @@
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.03933123314995651</v>
+        <v>0.004622313530222172</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.0697243002278853</v>
+        <v>-0.01392062903196596</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.1148653205109157</v>
+        <v>0.03895238083678559</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
@@ -5698,25 +5698,25 @@
         <v>-0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.2853915324477782</v>
+        <v>-0.001404366213316552</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0.0141538644880132</v>
+        <v>-0.006119523218412001</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.02442027992203946</v>
+        <v>0.004338953610945345</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.03878652207286696</v>
+        <v>-0.008018128258197357</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5740,10 +5740,10 @@
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0.01281191340219709</v>
+        <v>-0.0004605882264562096</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0.01499076722529284</v>
+        <v>0.005114609145617928</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
@@ -5752,13 +5752,13 @@
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.03241438944417869</v>
+        <v>0.01313232461773008</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5767,64 +5767,64 @@
         <v>-0</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.04272990936288708</v>
+        <v>0.003768833201529802</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.08663130022375884</v>
+        <v>0.03320038019476212</v>
       </c>
       <c r="BW10" t="n">
         <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.1196794578746276</v>
+        <v>0.0164253318497028</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.004986045684197062</v>
+        <v>0.01341145319002041</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.02987008051783608</v>
+        <v>-0.01454482856348326</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
         <v>0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.02245960358984975</v>
+        <v>-0.004662603646959067</v>
       </c>
       <c r="CI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ10" t="n">
         <v>-0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL10" t="n">
         <v>-0</v>
       </c>
       <c r="CM10" t="n">
-        <v>-0.02371609631305204</v>
+        <v>0.004401044784714811</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.005952956271636689</v>
+        <v>-0.03919340373823432</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
@@ -5833,52 +5833,52 @@
         <v>0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.1439965061558588</v>
+        <v>0.004632673725881478</v>
       </c>
       <c r="CR10" t="n">
         <v>-0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0.009630688207392038</v>
+        <v>0.01153407727347747</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.03845827014123514</v>
+        <v>-0.01586936524989101</v>
       </c>
       <c r="CX10" t="n">
         <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.01466182507189957</v>
+        <v>-0.006921001216357254</v>
       </c>
       <c r="DA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB10" t="n">
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD10" t="n">
         <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0.01123540061619606</v>
+        <v>0.008952824158613551</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.06220181761480455</v>
+        <v>-0.0216598212957308</v>
       </c>
       <c r="DG10" t="n">
         <v>-0</v>
@@ -5887,25 +5887,25 @@
         <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.005433084668339657</v>
+        <v>-0.008143161311541086</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
         <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0.0001442760876283015</v>
+        <v>0.008222344247134373</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.01198222854175798</v>
+        <v>-0.01045678555593841</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
@@ -5914,7 +5914,7 @@
         <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.03411696293192832</v>
+        <v>-0.0125803590097371</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -5926,52 +5926,52 @@
         <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW10" t="n">
-        <v>-0.01195062849133552</v>
+        <v>0.007124775244257421</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.04083884609361354</v>
+        <v>0.01872222937079536</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.0211421745334782</v>
+        <v>-0.006502794485653465</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
         <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
         <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0.01493725838951873</v>
+        <v>-0.006358770758413761</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.01099711738650835</v>
+        <v>0.002542488440491976</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
         <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>-0.01585768727483115</v>
+        <v>-0.00778119491767621</v>
       </c>
       <c r="EK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL10" t="n">
         <v>-0</v>
@@ -5983,19 +5983,19 @@
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>-0.01756786141767435</v>
+        <v>0.007853343993353749</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.05215538697376082</v>
+        <v>-0.004660866563504871</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER10" t="n">
         <v>0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.03659976062065428</v>
+        <v>-0.01176398309295114</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
@@ -6004,16 +6004,16 @@
         <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0.002904160431751409</v>
+        <v>0.01346350662543971</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.0470923639125823</v>
+        <v>-0.01976436914297753</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
@@ -6022,25 +6022,25 @@
         <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.0358861603886226</v>
+        <v>-0.008331212108671965</v>
       </c>
       <c r="FC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD10" t="n">
         <v>-0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF10" t="n">
         <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.01853661021055476</v>
+        <v>0.00341130576569573</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.01983234518673202</v>
+        <v>-0.007425627823980889</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
@@ -6049,7 +6049,7 @@
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.02418301524969638</v>
+        <v>0.001532161645637522</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
@@ -6058,28 +6058,28 @@
         <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO10" t="n">
         <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.007890386342076934</v>
+        <v>-0.00259180999521374</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.007988123690740919</v>
+        <v>0.002254399952386043</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.004868140387454056</v>
+        <v>0.001914775296193729</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
@@ -6091,10 +6091,10 @@
         <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0.02091922737966232</v>
+        <v>0.004352016271732067</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.02306414793179909</v>
+        <v>-0.01138641387585439</v>
       </c>
       <c r="GA10" t="n">
         <v>-0</v>
@@ -6103,10 +6103,10 @@
         <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
@@ -6115,7 +6115,7 @@
         <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,22 +6123,22 @@
         <v>-0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1785046798476037</v>
+        <v>0.05315655584430402</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1011240181849975</v>
+        <v>-0.01975109106100654</v>
       </c>
       <c r="F11" t="n">
         <v>-0</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.08921416097625591</v>
+        <v>-0.004459657930922694</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -6147,10 +6147,10 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1146605621445007</v>
+        <v>0.06542742567535771</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,16 +6159,16 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1138726711277974</v>
+        <v>-0.02345731048707466</v>
       </c>
       <c r="O11" t="n">
         <v>-0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.08038421756435063</v>
+        <v>-0.01110676678484227</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -6177,88 +6177,88 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1142974043092486</v>
+        <v>0.01557633375163342</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1258208513533662</v>
+        <v>-0.002545289598606325</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.04642698997237598</v>
+        <v>0.004607033856036886</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1077036237954596</v>
+        <v>0.005768735992263788</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0397338197587508</v>
+        <v>-0.006429333229266924</v>
       </c>
       <c r="AG11" t="n">
         <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.0435743927978913</v>
+        <v>-0.002453666890609954</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
         <v>-0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.02247827783789817</v>
+        <v>0.04733802559063871</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
         <v>-0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.01484923290495412</v>
+        <v>0.02533507135413585</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.05222886367939059</v>
+        <v>0.001015799902716527</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
         <v>-0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.3108957172100025</v>
+        <v>0.08839966444163126</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
@@ -6267,13 +6267,13 @@
         <v>-0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.08033776194292643</v>
+        <v>-0.006143325445976706</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.1102654669908945</v>
+        <v>-0.003730119834614813</v>
       </c>
       <c r="BA11" t="n">
         <v>0</v>
@@ -6282,10 +6282,10 @@
         <v>-0</v>
       </c>
       <c r="BC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.007418405768309454</v>
+        <v>-0.01722165251950683</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,40 +6294,40 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.04370599541842352</v>
+        <v>-0.01505172898158007</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0.03539031688232517</v>
+        <v>-9.727333933233993e-05</v>
       </c>
       <c r="BJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>-0.02506582837896245</v>
+        <v>-0.007693081417252733</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.06817561711852797</v>
+        <v>0.01361001327694475</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0.01837828693482495</v>
+        <v>0.003485039494341276</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
@@ -6336,52 +6336,52 @@
         <v>-0</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1126971464200718</v>
+        <v>0.06280889936718605</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.04793707737857879</v>
+        <v>-0.003618401560789846</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
       </c>
       <c r="CA11" t="n">
-        <v>-0.08853133347795433</v>
+        <v>0.003991559916657689</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.07908170389997242</v>
+        <v>-0.03877674207131927</v>
       </c>
       <c r="CF11" t="n">
         <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.04742240192910694</v>
+        <v>0.008444151677414189</v>
       </c>
       <c r="CI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.0335648089498736</v>
+        <v>0.004503892626658364</v>
       </c>
       <c r="CK11" t="n">
         <v>-0</v>
@@ -6393,7 +6393,7 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.1189921463028063</v>
+        <v>-0.04496695694199836</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
@@ -6402,13 +6402,13 @@
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.1096050730752053</v>
+        <v>0.01051257628345201</v>
       </c>
       <c r="CR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS11" t="n">
-        <v>-0.006233813667476117</v>
+        <v>-0.006773232955464526</v>
       </c>
       <c r="CT11" t="n">
         <v>-0</v>
@@ -6417,25 +6417,25 @@
         <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.07481650613939161</v>
+        <v>-0.03811215087910769</v>
       </c>
       <c r="CX11" t="n">
         <v>0</v>
       </c>
       <c r="CY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.04737039554608927</v>
+        <v>0.006744949903213085</v>
       </c>
       <c r="DA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.02425499860670514</v>
+        <v>0.007245207079909053</v>
       </c>
       <c r="DC11" t="n">
         <v>0</v>
@@ -6444,10 +6444,10 @@
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.1840595309398967</v>
+        <v>-0.01284581539781581</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
@@ -6456,25 +6456,25 @@
         <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.1195617669727142</v>
+        <v>-0.000121500515031442</v>
       </c>
       <c r="DJ11" t="n">
         <v>-0</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.05003249230876066</v>
+        <v>-0.00360564949678505</v>
       </c>
       <c r="DL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.04276345454727096</v>
+        <v>-0.01648260452829112</v>
       </c>
       <c r="DP11" t="n">
         <v>0</v>
@@ -6483,40 +6483,40 @@
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.03394559552577015</v>
+        <v>-0.01378182510406931</v>
       </c>
       <c r="DS11" t="n">
         <v>-0</v>
       </c>
       <c r="DT11" t="n">
-        <v>-0.01203126480662839</v>
+        <v>0.008527500536180364</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW11" t="n">
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.1733551390592918</v>
+        <v>0.02357703589606839</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.0548110609965359</v>
+        <v>-0.01531392960941205</v>
       </c>
       <c r="EB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC11" t="n">
-        <v>-0.0325938485162261</v>
+        <v>-0.006772243651091654</v>
       </c>
       <c r="ED11" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
         <v>0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.0655472489138311</v>
+        <v>-0.03037957521333138</v>
       </c>
       <c r="EH11" t="n">
         <v>-0</v>
@@ -6537,13 +6537,13 @@
         <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.06210982276268877</v>
+        <v>0.007123305621428716</v>
       </c>
       <c r="EK11" t="n">
         <v>0</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.01270168676277139</v>
+        <v>0.001919727456259566</v>
       </c>
       <c r="EM11" t="n">
         <v>-0</v>
@@ -6555,49 +6555,49 @@
         <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.03653197364110965</v>
+        <v>-0.02715853911915481</v>
       </c>
       <c r="EQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.1031941628401613</v>
+        <v>0.01417285002592012</v>
       </c>
       <c r="ET11" t="n">
         <v>0</v>
       </c>
       <c r="EU11" t="n">
-        <v>-0.04886358282500369</v>
+        <v>-0.001795865071915135</v>
       </c>
       <c r="EV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW11" t="n">
         <v>-0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.08071110418958334</v>
+        <v>-0.04056417144634319</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.05407682817794566</v>
+        <v>0.004743614732601656</v>
       </c>
       <c r="FC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.007600791148586738</v>
+        <v>0.004479875677156082</v>
       </c>
       <c r="FE11" t="n">
         <v>-0</v>
@@ -6606,25 +6606,25 @@
         <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.01762686706988494</v>
+        <v>-0.01042586828455992</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.116122557503383</v>
+        <v>-0.007374061222310264</v>
       </c>
       <c r="FL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.04804441402627659</v>
+        <v>-0.0008411428017638916</v>
       </c>
       <c r="FN11" t="n">
         <v>-0</v>
@@ -6633,40 +6633,40 @@
         <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.01049000724143184</v>
+        <v>-0.00603222588217546</v>
       </c>
       <c r="FR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.002380062087484514</v>
+        <v>0.001481957298509425</v>
       </c>
       <c r="FU11" t="n">
         <v>-0</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0.0266838238370284</v>
+        <v>-0.01149710121984396</v>
       </c>
       <c r="FW11" t="n">
         <v>-0</v>
       </c>
       <c r="FX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.02780816533617944</v>
+        <v>-0.03691501855371009</v>
       </c>
       <c r="GA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
@@ -6675,16 +6675,16 @@
         <v>0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.175018206177619</v>
+        <v>-0.004008641301808485</v>
       </c>
       <c r="GF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -7261,22 +7261,22 @@
         <v>-0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5948710414623353</v>
+        <v>0.5207419768086861</v>
       </c>
       <c r="C13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4905156353549016</v>
+        <v>-0.2482321684577299</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.007046673409549309</v>
+        <v>-0.08616561633984893</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
         <v>-0</v>
@@ -7285,25 +7285,25 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4530187170484563</v>
+        <v>0.451144992926927</v>
       </c>
       <c r="L13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.493045108268875</v>
+        <v>-0.4183378598619776</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1028440164336167</v>
+        <v>-0.1601051081344165</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -7315,19 +7315,19 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1789672710650844</v>
+        <v>0.1403631005471054</v>
       </c>
       <c r="U13" t="n">
         <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>-7.287313811222757e-05</v>
+        <v>-0.04951877806795748</v>
       </c>
       <c r="W13" t="n">
-        <v>0.08936667322856777</v>
+        <v>0.002726322412044506</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
@@ -7339,25 +7339,25 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.1960716684295707</v>
+        <v>0.06502506026499161</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.01333848021050101</v>
+        <v>-0.1211867640090165</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.001180045459792389</v>
+        <v>-0.04804404340015906</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>-0</v>
@@ -7366,25 +7366,25 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.04537591167584928</v>
+        <v>0.3481550541767631</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.1243247974812926</v>
+        <v>-0.02289476615584021</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.04623843788371839</v>
+        <v>0.2629866364696311</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7396,43 +7396,43 @@
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.7384258827499685</v>
+        <v>0.6862392357410299</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.06071143024961932</v>
+        <v>-0.1683650383336413</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.3666448814236962</v>
+        <v>-0.2411768967366279</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA13" t="n">
         <v>-0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.06711127037651697</v>
+        <v>-0.1136123009844611</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>-0.2469875809241023</v>
+        <v>-0.04803403942843423</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1754387097150564</v>
+        <v>-0.04395194914438657</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
@@ -7447,25 +7447,25 @@
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.06646150015538289</v>
+        <v>-0.0632075011396023</v>
       </c>
       <c r="BN13" t="n">
         <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.06223538080683845</v>
+        <v>-0.03749331466356663</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.1146040351390344</v>
+        <v>0.04071945538771221</v>
       </c>
       <c r="BQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
@@ -7477,22 +7477,22 @@
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.3418176075746268</v>
+        <v>0.4502778883616234</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>-0.02895795810477025</v>
+        <v>-0.2371683629955358</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.1681002172185761</v>
+        <v>-0.05280479794611575</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB13" t="n">
         <v>-0</v>
@@ -7504,16 +7504,16 @@
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.1598575756393334</v>
+        <v>-0.2413625061813212</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.1141888573388429</v>
+        <v>0.1163870246158109</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.07132402229706354</v>
+        <v>-0.001049348225050316</v>
       </c>
       <c r="CI13" t="n">
         <v>0</v>
@@ -7522,7 +7522,7 @@
         <v>-0</v>
       </c>
       <c r="CK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL13" t="n">
         <v>-0</v>
@@ -7531,19 +7531,19 @@
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.08543481171380005</v>
+        <v>-0.2139207895348953</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0.1674022271397673</v>
+        <v>0.2106686988433334</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.2854076623839079</v>
+        <v>0.1138523653249754</v>
       </c>
       <c r="CR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7555,19 +7555,19 @@
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.1555870362555829</v>
+        <v>-0.2478562574093074</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.1472586463877955</v>
+        <v>0.1307518845597365</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.05309973758023068</v>
+        <v>0.02215885777192684</v>
       </c>
       <c r="DA13" t="n">
         <v>-0</v>
@@ -7576,7 +7576,7 @@
         <v>0</v>
       </c>
       <c r="DC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD13" t="n">
         <v>0</v>
@@ -7585,25 +7585,25 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.07308260330986045</v>
+        <v>-0.0978537613511134</v>
       </c>
       <c r="DG13" t="n">
         <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.09452508195977237</v>
+        <v>0.1476230437616064</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.05720096979177479</v>
+        <v>0.01534675128641835</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM13" t="n">
         <v>0</v>
@@ -7612,25 +7612,25 @@
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.06324730068560709</v>
+        <v>-0.1074534220185053</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0.003282591798654456</v>
+        <v>0.07529647824614294</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.06443003001644705</v>
+        <v>-0.07356363721119202</v>
       </c>
       <c r="DS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
         <v>0</v>
@@ -7639,43 +7639,43 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.09342712663316595</v>
+        <v>0.1561782123288147</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0.005084558606347564</v>
+        <v>0.151935939596235</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.003757761174062269</v>
+        <v>-0.07783551542152257</v>
       </c>
       <c r="EB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
         <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.106901326150217</v>
+        <v>-0.2247219363829774</v>
       </c>
       <c r="EH13" t="n">
         <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.08703353569077581</v>
+        <v>0.08840894210356327</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.1066098283220194</v>
+        <v>0.004465265530807886</v>
       </c>
       <c r="EK13" t="n">
         <v>0</v>
@@ -7684,31 +7684,31 @@
         <v>-0</v>
       </c>
       <c r="EM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO13" t="n">
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.1418742156319603</v>
+        <v>-0.1424211684102908</v>
       </c>
       <c r="EQ13" t="n">
         <v>0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.1359584433553625</v>
+        <v>0.06107367036085291</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.1101532271037514</v>
+        <v>-0.02444670717227728</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
@@ -7720,70 +7720,70 @@
         <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.1662281220465378</v>
+        <v>-0.2811566478614512</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.1260509765001623</v>
+        <v>0.1484216634874905</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.06221891891025013</v>
+        <v>0.008146844754933585</v>
       </c>
       <c r="FC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD13" t="n">
         <v>-0</v>
       </c>
       <c r="FE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.01248709575865695</v>
+        <v>-0.08670757935392941</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>-0.1093221746958232</v>
+        <v>0.003642869264251637</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.02585126673133557</v>
+        <v>-0.03473813994014147</v>
       </c>
       <c r="FL13" t="n">
         <v>-0</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.01494756187010781</v>
+        <v>-0.1681291461934463</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.04930837211661783</v>
+        <v>0.1988570239662695</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.03809630709699297</v>
+        <v>0.02680748446442141</v>
       </c>
       <c r="FU13" t="n">
         <v>-0</v>
@@ -7798,28 +7798,28 @@
         <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.05314578132219317</v>
+        <v>-0.2335122078040252</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0.08619734626087625</v>
+        <v>0.06593141403258508</v>
       </c>
       <c r="GC13" t="n">
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
         <v>-0</v>
@@ -8396,52 +8396,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.06158543720380951</v>
+        <v>0.1640246001844684</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.2568787567367155</v>
+        <v>-0.3244827258473774</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2483844190114496</v>
+        <v>0.09382245154375307</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0947505837108769</v>
+        <v>0.06838104968244302</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I15" t="n">
         <v>-0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.04853631769757778</v>
+        <v>0.0982645571104248</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2034252051278128</v>
+        <v>-0.4187658285726916</v>
       </c>
       <c r="L15" t="n">
         <v>-0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2296327252036461</v>
+        <v>0.03560068632149786</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1686160811551274</v>
+        <v>0.08475976302625875</v>
       </c>
       <c r="O15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q15" t="n">
         <v>-0</v>
@@ -8450,19 +8450,19 @@
         <v>-0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.004740681059533958</v>
+        <v>0.008896691241534554</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.09259413498656605</v>
+        <v>0.003013854871572844</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.04317870561955803</v>
+        <v>0.02775586146508308</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.0004349151815475106</v>
+        <v>0.01854333076822673</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -8477,46 +8477,46 @@
         <v>-0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.01510958498229509</v>
+        <v>0.05419336425389866</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.08436830842687859</v>
+        <v>0.03811196882407793</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.1110556191324819</v>
+        <v>0.1633801666362942</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.08089558794058159</v>
+        <v>0.09800716304653639</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.02594992922587766</v>
+        <v>0.04012606204854596</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.05839210816672654</v>
+        <v>-0.1553542823176999</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.02525367753953126</v>
+        <v>0.07471083671003374</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.00789868512556606</v>
+        <v>-0.09267817568178847</v>
       </c>
       <c r="AP15" t="n">
         <v>-0</v>
@@ -8525,79 +8525,79 @@
         <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS15" t="n">
         <v>-0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0.01575224190118733</v>
+        <v>-0.03680700426703042</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.2604831897667804</v>
+        <v>-0.347855746200294</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.05458462507775435</v>
+        <v>-0.1761452391041343</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.1231732021087255</v>
+        <v>0.04929298670451623</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB15" t="n">
         <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.01755722313905271</v>
+        <v>0.0409943107373664</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.02464879687650252</v>
+        <v>-0.04362858267180943</v>
       </c>
       <c r="BE15" t="n">
         <v>-0</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.05232394570625434</v>
+        <v>0.09606754044206042</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.105909416316797</v>
+        <v>0.0002979244097812074</v>
       </c>
       <c r="BH15" t="n">
         <v>-0</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK15" t="n">
         <v>-0</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0.04510793831516071</v>
+        <v>-0.02502291348112453</v>
       </c>
       <c r="BM15" t="n">
-        <v>-0.02117588163422043</v>
+        <v>0.03590422274582059</v>
       </c>
       <c r="BN15" t="n">
         <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>-0.0062803333650185</v>
+        <v>-0.03343312004686631</v>
       </c>
       <c r="BP15" t="n">
-        <v>-0.05764185736737392</v>
+        <v>-0.1203191526320355</v>
       </c>
       <c r="BQ15" t="n">
         <v>0</v>
@@ -8612,22 +8612,22 @@
         <v>0</v>
       </c>
       <c r="BU15" t="n">
-        <v>-0.00816579116285608</v>
+        <v>-0.03441452178363825</v>
       </c>
       <c r="BV15" t="n">
-        <v>-0.1987738064183862</v>
+        <v>-0.2991043006327472</v>
       </c>
       <c r="BW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.0489127523529741</v>
+        <v>-0.05281997327181602</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.04311556127315788</v>
+        <v>-0.03870919475719577</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA15" t="n">
         <v>0</v>
@@ -8639,49 +8639,49 @@
         <v>-0</v>
       </c>
       <c r="CD15" t="n">
-        <v>-0.007114608475298875</v>
+        <v>-0.05632455757947322</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.06842771163518011</v>
+        <v>0.1544823895402798</v>
       </c>
       <c r="CF15" t="n">
         <v>0</v>
       </c>
       <c r="CG15" t="n">
-        <v>-0.05226672932914687</v>
+        <v>-0.007922629797909191</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.002920021256033724</v>
+        <v>-0.04540407532440793</v>
       </c>
       <c r="CI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ15" t="n">
         <v>0</v>
       </c>
       <c r="CK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL15" t="n">
         <v>0</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.08718932089113511</v>
+        <v>0.1417730151835269</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.02524393181074396</v>
+        <v>0.3096014230025778</v>
       </c>
       <c r="CO15" t="n">
         <v>0</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.1224393766769888</v>
+        <v>0.1621585786151585</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.1650596660151444</v>
+        <v>0.02672219298348465</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS15" t="n">
         <v>0</v>
@@ -8690,22 +8690,22 @@
         <v>0</v>
       </c>
       <c r="CU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV15" t="n">
-        <v>-0.01752062902851139</v>
+        <v>-0.04554443612985605</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.07965085135626859</v>
+        <v>0.1416820656566735</v>
       </c>
       <c r="CX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY15" t="n">
-        <v>-0.05517996552383837</v>
+        <v>-0.005535094711704349</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.004463807293546855</v>
+        <v>-0.04096276898580697</v>
       </c>
       <c r="DA15" t="n">
         <v>-0</v>
@@ -8714,133 +8714,133 @@
         <v>-0</v>
       </c>
       <c r="DC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD15" t="n">
         <v>-0</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.009586366568377611</v>
+        <v>0.06458016065902902</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.1321849925390954</v>
+        <v>0.09315516459573595</v>
       </c>
       <c r="DG15" t="n">
         <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0.07470263943144215</v>
+        <v>-0.004940353515357162</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.1033057539329563</v>
+        <v>0.05077760717315101</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL15" t="n">
         <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0.05228279944384388</v>
+        <v>0.03043863235809877</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.05051349123572043</v>
+        <v>0.09377439702135014</v>
       </c>
       <c r="DP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.05103306263361203</v>
+        <v>0.1100365874734746</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.04219583481755008</v>
+        <v>-0.07526602198657861</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
       </c>
       <c r="DT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.03406256178744193</v>
+        <v>-0.05289614273482057</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.07897216355159074</v>
+        <v>-0.193873516758183</v>
       </c>
       <c r="DY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0.01165496980131522</v>
+        <v>0.02717755622147565</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.1106738884153937</v>
+        <v>0.2111988039561225</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC15" t="n">
         <v>0</v>
       </c>
       <c r="ED15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.00218608187986711</v>
+        <v>0.09954737376380514</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.04755132627783627</v>
+        <v>0.1155669335940619</v>
       </c>
       <c r="EH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI15" t="n">
-        <v>-0.08845207483117679</v>
+        <v>0.05676001716572657</v>
       </c>
       <c r="EJ15" t="n">
-        <v>-0.07903456456962063</v>
+        <v>-0.07932219204642267</v>
       </c>
       <c r="EK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL15" t="n">
         <v>0</v>
       </c>
       <c r="EM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN15" t="n">
         <v>0</v>
       </c>
       <c r="EO15" t="n">
-        <v>-0.01041058376319638</v>
+        <v>-0.009036762914087847</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.08743717953039011</v>
+        <v>0.02753208373526301</v>
       </c>
       <c r="EQ15" t="n">
         <v>0</v>
       </c>
       <c r="ER15" t="n">
-        <v>-0.01608663347744821</v>
+        <v>0.03399268073841828</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.1117136408819428</v>
+        <v>0.0920746781438546</v>
       </c>
       <c r="ET15" t="n">
         <v>0</v>
@@ -8852,22 +8852,22 @@
         <v>0</v>
       </c>
       <c r="EW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX15" t="n">
-        <v>-0.0008196173120676843</v>
+        <v>-0.05213654431039382</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.08732224050556528</v>
+        <v>0.1670662409390642</v>
       </c>
       <c r="EZ15" t="n">
         <v>0</v>
       </c>
       <c r="FA15" t="n">
-        <v>-0.06209006195716083</v>
+        <v>0.0191429998116882</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.005697004659121195</v>
+        <v>-0.03526144162310503</v>
       </c>
       <c r="FC15" t="n">
         <v>0</v>
@@ -8876,91 +8876,91 @@
         <v>0</v>
       </c>
       <c r="FE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF15" t="n">
         <v>0</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.01147247245720538</v>
+        <v>-0.01243731204642162</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.04703011338060811</v>
+        <v>-0.02727426955652213</v>
       </c>
       <c r="FI15" t="n">
         <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>-0.00336335036528155</v>
+        <v>-0.001778379435201822</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.01894005075716839</v>
+        <v>0.134705480031467</v>
       </c>
       <c r="FL15" t="n">
         <v>-0</v>
       </c>
       <c r="FM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
         <v>0</v>
       </c>
       <c r="FP15" t="n">
-        <v>-0.00622799783484881</v>
+        <v>-0.101719677749087</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.07179744759816743</v>
+        <v>0.03094077118790559</v>
       </c>
       <c r="FR15" t="n">
         <v>0</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.01247609879506104</v>
+        <v>0.1056596294718048</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.02782927530315671</v>
+        <v>-0.03157732679845121</v>
       </c>
       <c r="FU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW15" t="n">
         <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.02477814617265395</v>
+        <v>-0.03049812795222524</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.03984431038860908</v>
+        <v>0.1536336761134848</v>
       </c>
       <c r="GA15" t="n">
         <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.08910460664488494</v>
+        <v>0.06254221031259176</v>
       </c>
       <c r="GC15" t="n">
         <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE15" t="n">
         <v>0</v>
       </c>
       <c r="GF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="16">
@@ -9534,19 +9534,19 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.2398384557045477</v>
+        <v>0.06427493313461162</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.07644348835367878</v>
+        <v>-0.01277430210113692</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.04877893475828808</v>
+        <v>-0.02936289614125796</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -9561,19 +9561,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1784115108051133</v>
+        <v>0.07077782373069673</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.07085021039299262</v>
+        <v>-0.01870968219321682</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.07476628175319974</v>
+        <v>-0.03162345756434293</v>
       </c>
       <c r="O17" t="n">
         <v>-0</v>
@@ -9591,70 +9591,70 @@
         <v>-0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.06026678472955602</v>
+        <v>0.01727240628784451</v>
       </c>
       <c r="U17" t="n">
-        <v>0.004347233298472292</v>
+        <v>0.001316621369637516</v>
       </c>
       <c r="V17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02711378935442116</v>
+        <v>0.02207494558326294</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.0910282755046668</v>
+        <v>-0.002709559530874456</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.008635445619820881</v>
+        <v>-0.02346823321191394</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.01888214181707426</v>
+        <v>-0.01828250193945796</v>
       </c>
       <c r="AG17" t="n">
         <v>-0</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ17" t="n">
         <v>-0</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.067657959060381</v>
+        <v>0.03708326978456185</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0.002654454202091233</v>
+        <v>-0.003448093084324726</v>
       </c>
       <c r="AN17" t="n">
         <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.006041817403398927</v>
+        <v>0.03172370936530858</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
         <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS17" t="n">
         <v>0</v>
@@ -9672,25 +9672,25 @@
         <v>-0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.1702791757022311</v>
+        <v>0.07540436497661136</v>
       </c>
       <c r="AV17" t="n">
-        <v>-0.06533891323990954</v>
+        <v>-5.028010312800128e-05</v>
       </c>
       <c r="AW17" t="n">
         <v>-0</v>
       </c>
       <c r="AX17" t="n">
-        <v>-0.0003375130653438004</v>
+        <v>-0.0123436190492489</v>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB17" t="n">
         <v>0</v>
@@ -9699,16 +9699,16 @@
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.05332838448696533</v>
+        <v>-0.00974271237068473</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0.01648767178533172</v>
+        <v>-0.008072354490693911</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.07514030707675212</v>
+        <v>-0.0322037970172454</v>
       </c>
       <c r="BH17" t="n">
         <v>-0</v>
@@ -9717,7 +9717,7 @@
         <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
@@ -9726,25 +9726,25 @@
         <v>-0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.02175261323490733</v>
+        <v>-0.003162160564878848</v>
       </c>
       <c r="BN17" t="n">
-        <v>-0.01633080816659486</v>
+        <v>-0.007926166149425285</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.01566462293026832</v>
+        <v>0.01135688299666091</v>
       </c>
       <c r="BQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR17" t="n">
         <v>-0</v>
       </c>
       <c r="BS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT17" t="n">
         <v>-0</v>
@@ -9753,22 +9753,22 @@
         <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.0950813629746724</v>
+        <v>0.05960381706907564</v>
       </c>
       <c r="BW17" t="n">
-        <v>-0.1014190375745772</v>
+        <v>-0.003143056569369571</v>
       </c>
       <c r="BX17" t="n">
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.008244200459112531</v>
+        <v>0.0162133850181138</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB17" t="n">
         <v>0</v>
@@ -9777,28 +9777,28 @@
         <v>0</v>
       </c>
       <c r="CD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.05532319639130551</v>
+        <v>-0.03038806375599338</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.01284461458286222</v>
+        <v>0.009709660916727125</v>
       </c>
       <c r="CG17" t="n">
         <v>0</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.008746703004016448</v>
+        <v>0.009850864255203068</v>
       </c>
       <c r="CI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ17" t="n">
         <v>-0</v>
       </c>
       <c r="CK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL17" t="n">
         <v>-0</v>
@@ -9807,16 +9807,16 @@
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.00301023106605983</v>
+        <v>-0.04939403436664244</v>
       </c>
       <c r="CO17" t="n">
-        <v>-0.01600269910182585</v>
+        <v>0.0194607101100778</v>
       </c>
       <c r="CP17" t="n">
         <v>-0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.02128087712730854</v>
+        <v>0.01690172285158181</v>
       </c>
       <c r="CR17" t="n">
         <v>0</v>
@@ -9831,25 +9831,25 @@
         <v>0</v>
       </c>
       <c r="CV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.04549229949119259</v>
+        <v>-0.02737489373119687</v>
       </c>
       <c r="CX17" t="n">
-        <v>0.004348518636704176</v>
+        <v>0.008096296500482521</v>
       </c>
       <c r="CY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.006092213544984015</v>
+        <v>0.006202739366212013</v>
       </c>
       <c r="DA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC17" t="n">
         <v>0</v>
@@ -9861,16 +9861,16 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.05963675613430092</v>
+        <v>-0.01477041654920598</v>
       </c>
       <c r="DG17" t="n">
-        <v>-0.01009442433619464</v>
+        <v>0.0009597906794282979</v>
       </c>
       <c r="DH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.01083370168653529</v>
+        <v>0.002661545786768549</v>
       </c>
       <c r="DJ17" t="n">
         <v>-0</v>
@@ -9882,52 +9882,52 @@
         <v>0</v>
       </c>
       <c r="DM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN17" t="n">
         <v>-0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.03135272012083146</v>
+        <v>-0.01775689462842542</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.009170342474947617</v>
+        <v>-0.00479948431859539</v>
       </c>
       <c r="DQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>-0.01187694382015031</v>
+        <v>0.0186242165726466</v>
       </c>
       <c r="DS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT17" t="n">
         <v>0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.03112887624128271</v>
+        <v>0.02233113993664863</v>
       </c>
       <c r="DY17" t="n">
-        <v>-0.01040311103565983</v>
+        <v>0.008343490347967509</v>
       </c>
       <c r="DZ17" t="n">
         <v>0</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.01318963520911242</v>
+        <v>-0.01578313078207211</v>
       </c>
       <c r="EB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC17" t="n">
         <v>0</v>
@@ -9939,46 +9939,46 @@
         <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.01494603235815253</v>
+        <v>-0.01560160664778748</v>
       </c>
       <c r="EH17" t="n">
-        <v>0.00586969846035558</v>
+        <v>-0.003935454725257533</v>
       </c>
       <c r="EI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.03976967238533899</v>
+        <v>0.00232064253542598</v>
       </c>
       <c r="EK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.0151797607451314</v>
+        <v>-0.02307174851610377</v>
       </c>
       <c r="EQ17" t="n">
-        <v>-0.03112043808212235</v>
+        <v>0.001053096223101525</v>
       </c>
       <c r="ER17" t="n">
         <v>-0</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.02494848899549644</v>
+        <v>-0.001115524784416534</v>
       </c>
       <c r="ET17" t="n">
         <v>0</v>
@@ -9987,34 +9987,34 @@
         <v>-0</v>
       </c>
       <c r="EV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW17" t="n">
         <v>-0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.05046796137321236</v>
+        <v>-0.03241790077846064</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0.006334453657450717</v>
+        <v>0.00812273679826357</v>
       </c>
       <c r="FA17" t="n">
         <v>0</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.009538711560721237</v>
+        <v>0.006252571649659322</v>
       </c>
       <c r="FC17" t="n">
         <v>-0</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF17" t="n">
         <v>-0</v>
@@ -10023,49 +10023,49 @@
         <v>-0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.03802849455277247</v>
+        <v>-0.001498685310951343</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0.02171963042296305</v>
+        <v>-0.02025566847441851</v>
       </c>
       <c r="FJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.0639618921848934</v>
+        <v>-0.02073289510630649</v>
       </c>
       <c r="FL17" t="n">
         <v>-0</v>
       </c>
       <c r="FM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.004850340553340759</v>
+        <v>-0.004949454793908877</v>
       </c>
       <c r="FR17" t="n">
-        <v>0.05936964152463652</v>
+        <v>0.006079069422971485</v>
       </c>
       <c r="FS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT17" t="n">
-        <v>-0.004407581977747275</v>
+        <v>0.01445119967103113</v>
       </c>
       <c r="FU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW17" t="n">
         <v>0</v>
@@ -10074,28 +10074,28 @@
         <v>0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.01586017454117757</v>
+        <v>-0.02202919283236673</v>
       </c>
       <c r="GA17" t="n">
-        <v>0.01711610929425121</v>
+        <v>-0.01179288345349901</v>
       </c>
       <c r="GB17" t="n">
         <v>0</v>
       </c>
       <c r="GC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
         <v>0</v>
@@ -10106,49 +10106,49 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5157750032943882</v>
+        <v>0.5477744545253871</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.156949117483222</v>
+        <v>-0.2909676108898208</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1370108903756533</v>
+        <v>-0.03813437769141905</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H18" t="n">
         <v>-0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3362885949047871</v>
+        <v>0.5614034341673927</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1460239229034258</v>
+        <v>-0.4140111300854307</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1179078484323896</v>
+        <v>-0.1066649727327939</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -10157,73 +10157,73 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1048334945480313</v>
+        <v>0.07066864173211374</v>
       </c>
       <c r="U18" t="n">
         <v>-0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.02352697756147575</v>
+        <v>-0.1148709236844845</v>
       </c>
       <c r="W18" t="n">
-        <v>0.01501302414736853</v>
+        <v>-0.09241685485525244</v>
       </c>
       <c r="X18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.07267963137666765</v>
+        <v>-0.04477468273701007</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.009437410999191428</v>
+        <v>-0.1951400390396806</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.02565613218704321</v>
+        <v>-0.0739863861285564</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.02581446745005415</v>
+        <v>0.2013238997644578</v>
       </c>
       <c r="AM18" t="n">
         <v>-0</v>
       </c>
       <c r="AN18" t="n">
-        <v>-0.06999417196344883</v>
+        <v>-0.09805001742327721</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.07203487311131802</v>
+        <v>0.1494279337524936</v>
       </c>
       <c r="AP18" t="n">
         <v>0</v>
@@ -10238,28 +10238,28 @@
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.3979977432930662</v>
+        <v>0.5528858804039491</v>
       </c>
       <c r="AV18" t="n">
         <v>-0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.01319234158374147</v>
+        <v>-0.1053775234408125</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.02319527281148482</v>
+        <v>-0.1732059018081423</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
         <v>-0</v>
@@ -10268,16 +10268,16 @@
         <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.03747458154240559</v>
+        <v>-0.01928764015751389</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>-0.08687484100822811</v>
+        <v>-0.05753068906471086</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.1494657634247288</v>
+        <v>-0.0664339163409307</v>
       </c>
       <c r="BH18" t="n">
         <v>0</v>
@@ -10286,25 +10286,25 @@
         <v>-0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.08399194826006862</v>
+        <v>-0.0233423699840716</v>
       </c>
       <c r="BN18" t="n">
         <v>-0</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.05277388412088758</v>
+        <v>-0.01187666559040243</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.1136768850193044</v>
+        <v>0.05865562629041021</v>
       </c>
       <c r="BQ18" t="n">
         <v>-0</v>
@@ -10319,49 +10319,49 @@
         <v>-0</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.2119164342588889</v>
+        <v>0.3831020152623137</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.0254016593295565</v>
+        <v>-0.1716178883328798</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.002357622305919571</v>
+        <v>-0.05268747629228786</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA18" t="n">
         <v>-0</v>
       </c>
       <c r="CB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.1074638059224669</v>
+        <v>-0.189770113151265</v>
       </c>
       <c r="CF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG18" t="n">
-        <v>0.01428195178383901</v>
+        <v>0.1177472311906058</v>
       </c>
       <c r="CH18" t="n">
-        <v>-0.01560715776950641</v>
+        <v>0.01998739808673766</v>
       </c>
       <c r="CI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ18" t="n">
         <v>-0</v>
@@ -10370,25 +10370,25 @@
         <v>0</v>
       </c>
       <c r="CL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM18" t="n">
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>0.02003337904687891</v>
+        <v>-0.2273892704236985</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
       </c>
       <c r="CP18" t="n">
-        <v>-0.07516436320363074</v>
+        <v>0.2497036436155836</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.1092785681797442</v>
+        <v>0.1096586410371434</v>
       </c>
       <c r="CR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS18" t="n">
         <v>-0</v>
@@ -10397,25 +10397,25 @@
         <v>-0</v>
       </c>
       <c r="CU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV18" t="n">
         <v>-0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.0983494713341803</v>
+        <v>-0.1918363752319062</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
-        <v>0.03470662745948894</v>
+        <v>0.1365225264820335</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-0.02211896485695158</v>
+        <v>0.01256597624992136</v>
       </c>
       <c r="DA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB18" t="n">
         <v>0</v>
@@ -10424,28 +10424,28 @@
         <v>-0</v>
       </c>
       <c r="DD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.05364528142549455</v>
+        <v>-0.06809066427660955</v>
       </c>
       <c r="DG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.06307103859473767</v>
+        <v>0.02140826590889568</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.04578825415974611</v>
+        <v>-0.04078015296624996</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL18" t="n">
         <v>0</v>
@@ -10454,22 +10454,22 @@
         <v>0</v>
       </c>
       <c r="DN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.03857195646516095</v>
+        <v>-0.1572270969334095</v>
       </c>
       <c r="DP18" t="n">
         <v>0</v>
       </c>
       <c r="DQ18" t="n">
-        <v>0.07715282740479701</v>
+        <v>-0.01289453464977498</v>
       </c>
       <c r="DR18" t="n">
-        <v>-0.04791414814622841</v>
+        <v>0.07134396644321589</v>
       </c>
       <c r="DS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT18" t="n">
         <v>-0</v>
@@ -10481,55 +10481,55 @@
         <v>0</v>
       </c>
       <c r="DW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>0.05326798086464507</v>
+        <v>0.1616443923167656</v>
       </c>
       <c r="DY18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>0.01415626086764929</v>
+        <v>0.02403798203591901</v>
       </c>
       <c r="EA18" t="n">
-        <v>-0.06940490256883664</v>
+        <v>-0.1094449614976861</v>
       </c>
       <c r="EB18" t="n">
         <v>0</v>
       </c>
       <c r="EC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED18" t="n">
         <v>0</v>
       </c>
       <c r="EE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF18" t="n">
         <v>0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.08629303985328117</v>
+        <v>-0.1404500395109599</v>
       </c>
       <c r="EH18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI18" t="n">
-        <v>0.02898531552920333</v>
+        <v>0.09081752583845536</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.06293907663915696</v>
+        <v>0.04137913306420428</v>
       </c>
       <c r="EK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL18" t="n">
         <v>-0</v>
       </c>
       <c r="EM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN18" t="n">
         <v>-0</v>
@@ -10538,22 +10538,22 @@
         <v>0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.06103221538600631</v>
+        <v>-0.05045031540032782</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
-        <v>0.03021844281681699</v>
+        <v>0.101534648357324</v>
       </c>
       <c r="ES18" t="n">
-        <v>-0.01522337418427669</v>
+        <v>-0.06822453851143791</v>
       </c>
       <c r="ET18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV18" t="n">
         <v>0</v>
@@ -10562,46 +10562,46 @@
         <v>-0</v>
       </c>
       <c r="EX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.09611268043638599</v>
+        <v>-0.2082378942752172</v>
       </c>
       <c r="EZ18" t="n">
         <v>-0</v>
       </c>
       <c r="FA18" t="n">
-        <v>0.02335400379922379</v>
+        <v>0.1346295826968133</v>
       </c>
       <c r="FB18" t="n">
-        <v>-0.009420507010412176</v>
+        <v>0.003479035561423591</v>
       </c>
       <c r="FC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE18" t="n">
         <v>0</v>
       </c>
       <c r="FF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG18" t="n">
         <v>0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.01883771715616317</v>
+        <v>-0.02825443036361637</v>
       </c>
       <c r="FI18" t="n">
         <v>-0</v>
       </c>
       <c r="FJ18" t="n">
-        <v>0.06238513267608242</v>
+        <v>0.1226856412299585</v>
       </c>
       <c r="FK18" t="n">
-        <v>-0.06743560875527012</v>
+        <v>-0.1273866489763509</v>
       </c>
       <c r="FL18" t="n">
         <v>-0</v>
@@ -10613,58 +10613,58 @@
         <v>-0</v>
       </c>
       <c r="FO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>0.009329376402258715</v>
+        <v>-0.0870328313293306</v>
       </c>
       <c r="FR18" t="n">
         <v>-0</v>
       </c>
       <c r="FS18" t="n">
-        <v>0.03482936514784161</v>
+        <v>0.2223654466675604</v>
       </c>
       <c r="FT18" t="n">
-        <v>0.0166927950573163</v>
+        <v>0.06736602293852742</v>
       </c>
       <c r="FU18" t="n">
         <v>-0</v>
       </c>
       <c r="FV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX18" t="n">
         <v>0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>0.004491258658256692</v>
+        <v>-0.1549748752849563</v>
       </c>
       <c r="GA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB18" t="n">
-        <v>-0.04670833635973717</v>
+        <v>0.06646525742999251</v>
       </c>
       <c r="GC18" t="n">
         <v>0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE18" t="n">
         <v>-0</v>
       </c>
       <c r="GF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG18" t="n">
         <v>-0</v>
@@ -10675,16 +10675,16 @@
         <v>0</v>
       </c>
       <c r="B19" t="n">
-        <v>0.5100772222337645</v>
+        <v>0.0108814379017809</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4023577034995955</v>
+        <v>-0.006687437548049992</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -10693,16 +10693,16 @@
         <v>-0</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.001353687170208007</v>
+        <v>0.0003842552496994279</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3732204294963345</v>
+        <v>0.01019798231383899</v>
       </c>
       <c r="L19" t="n">
         <v>-0</v>
@@ -10711,7 +10711,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3627120644700591</v>
+        <v>-0.01201182686924047</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -10720,52 +10720,52 @@
         <v>-0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.07807988143763318</v>
+        <v>-0.001227656007243145</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1450368344360076</v>
+        <v>0.005599485651221012</v>
       </c>
       <c r="U19" t="n">
         <v>-0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.01947112381251759</v>
+        <v>-0.004143533543847782</v>
       </c>
       <c r="X19" t="n">
         <v>-0</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.06773682532023961</v>
+        <v>-0.002096738899974224</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.1681640070126529</v>
+        <v>-0.003744494464714007</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.1057202654728529</v>
+        <v>-0.009621201472140826</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -10774,16 +10774,16 @@
         <v>-0</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.0303868545797198</v>
+        <v>0.003358270931085093</v>
       </c>
       <c r="AJ19" t="n">
         <v>-0</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.1332801877284177</v>
+        <v>0.008182190590419428</v>
       </c>
       <c r="AM19" t="n">
         <v>0</v>
@@ -10792,7 +10792,7 @@
         <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>-0.04523594466554644</v>
+        <v>-0.001117954708158264</v>
       </c>
       <c r="AP19" t="n">
         <v>0</v>
@@ -10801,7 +10801,7 @@
         <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>-0.03903185375433166</v>
+        <v>0.001398520831536258</v>
       </c>
       <c r="AS19" t="n">
         <v>0</v>
@@ -10810,7 +10810,7 @@
         <v>-0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.5759134507225721</v>
+        <v>0.01419316262323325</v>
       </c>
       <c r="AV19" t="n">
         <v>-0</v>
@@ -10819,25 +10819,25 @@
         <v>-0</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.01118599730966722</v>
+        <v>-0.005169257267399616</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ19" t="n">
         <v>-0</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.1184802203629893</v>
+        <v>0.0006247551134038647</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC19" t="n">
         <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>0.002294146170999243</v>
+        <v>-0.004099979489602655</v>
       </c>
       <c r="BE19" t="n">
         <v>0</v>
@@ -10846,25 +10846,25 @@
         <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>-0.3136656464288252</v>
+        <v>-0.008230612220559159</v>
       </c>
       <c r="BH19" t="n">
         <v>0</v>
       </c>
       <c r="BI19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ19" t="n">
-        <v>-0.03813618522912114</v>
+        <v>-0.0007995312556031968</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.1786588929509977</v>
+        <v>0.006936438306243705</v>
       </c>
       <c r="BN19" t="n">
         <v>-0</v>
@@ -10873,16 +10873,16 @@
         <v>-0</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.1664621175214835</v>
+        <v>0.00690371022945284</v>
       </c>
       <c r="BQ19" t="n">
         <v>-0</v>
       </c>
       <c r="BR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS19" t="n">
-        <v>0.06972275107728707</v>
+        <v>0.001436442287807196</v>
       </c>
       <c r="BT19" t="n">
         <v>-0</v>
@@ -10891,16 +10891,16 @@
         <v>-0</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.3509231495822372</v>
+        <v>0.01498460135594569</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY19" t="n">
-        <v>-0.03796576949519391</v>
+        <v>-0.003149610738862781</v>
       </c>
       <c r="BZ19" t="n">
         <v>-0</v>
@@ -10909,106 +10909,106 @@
         <v>-0</v>
       </c>
       <c r="CB19" t="n">
-        <v>0.02795865231214099</v>
+        <v>-0.003560740458241749</v>
       </c>
       <c r="CC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD19" t="n">
         <v>-0</v>
       </c>
       <c r="CE19" t="n">
-        <v>-0.1019115583276873</v>
+        <v>-0.001405548592616287</v>
       </c>
       <c r="CF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG19" t="n">
         <v>-0</v>
       </c>
       <c r="CH19" t="n">
-        <v>0.04969754160370427</v>
+        <v>0.00158374347664439</v>
       </c>
       <c r="CI19" t="n">
         <v>-0</v>
       </c>
       <c r="CJ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK19" t="n">
-        <v>0.004908038484594537</v>
+        <v>0.001266887449312654</v>
       </c>
       <c r="CL19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM19" t="n">
         <v>0</v>
       </c>
       <c r="CN19" t="n">
-        <v>-0.1201311495044716</v>
+        <v>-0.003513486340154609</v>
       </c>
       <c r="CO19" t="n">
         <v>-0</v>
       </c>
       <c r="CP19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ19" t="n">
-        <v>-0.2198938461185696</v>
+        <v>0.007492005575751732</v>
       </c>
       <c r="CR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT19" t="n">
-        <v>-0.03633792064423156</v>
+        <v>0.004884996292318828</v>
       </c>
       <c r="CU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV19" t="n">
         <v>0</v>
       </c>
       <c r="CW19" t="n">
-        <v>-0.07128095363459042</v>
+        <v>-0.001315952067176746</v>
       </c>
       <c r="CX19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY19" t="n">
         <v>0</v>
       </c>
       <c r="CZ19" t="n">
-        <v>0.02438666350594522</v>
+        <v>0.002081954404355638</v>
       </c>
       <c r="DA19" t="n">
         <v>0</v>
       </c>
       <c r="DB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC19" t="n">
-        <v>-0.002030293114276204</v>
+        <v>0.001709767897347751</v>
       </c>
       <c r="DD19" t="n">
         <v>0</v>
       </c>
       <c r="DE19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>-0.1697491485024399</v>
+        <v>-0.001499160810765916</v>
       </c>
       <c r="DG19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.02735785168026065</v>
+        <v>0.002441961957912378</v>
       </c>
       <c r="DJ19" t="n">
         <v>-0</v>
@@ -11017,7 +11017,7 @@
         <v>0</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.003177402447494199</v>
+        <v>2.471819399214399e-05</v>
       </c>
       <c r="DM19" t="n">
         <v>-0</v>
@@ -11026,7 +11026,7 @@
         <v>-0</v>
       </c>
       <c r="DO19" t="n">
-        <v>-0.04130587611179686</v>
+        <v>-0.004516136922319243</v>
       </c>
       <c r="DP19" t="n">
         <v>-0</v>
@@ -11035,16 +11035,16 @@
         <v>0</v>
       </c>
       <c r="DR19" t="n">
-        <v>-0.0007819057649526998</v>
+        <v>6.186222180440633e-05</v>
       </c>
       <c r="DS19" t="n">
         <v>-0</v>
       </c>
       <c r="DT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU19" t="n">
-        <v>0.09392588783129278</v>
+        <v>0.001796734191354791</v>
       </c>
       <c r="DV19" t="n">
         <v>0</v>
@@ -11053,7 +11053,7 @@
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>-0.01311221096306797</v>
+        <v>0.0004632472377105768</v>
       </c>
       <c r="DY19" t="n">
         <v>0</v>
@@ -11062,34 +11062,34 @@
         <v>-0</v>
       </c>
       <c r="EA19" t="n">
-        <v>-0.0009084567326184659</v>
+        <v>-0.003814837415621189</v>
       </c>
       <c r="EB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC19" t="n">
         <v>0</v>
       </c>
       <c r="ED19" t="n">
-        <v>0.008440642080034545</v>
+        <v>-0.004948054158442947</v>
       </c>
       <c r="EE19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF19" t="n">
         <v>0</v>
       </c>
       <c r="EG19" t="n">
-        <v>-0.004821151538745808</v>
+        <v>0.004085568170016102</v>
       </c>
       <c r="EH19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ19" t="n">
-        <v>0.09084183660608049</v>
+        <v>-0.00293541271227393</v>
       </c>
       <c r="EK19" t="n">
         <v>-0</v>
@@ -11098,16 +11098,16 @@
         <v>-0</v>
       </c>
       <c r="EM19" t="n">
-        <v>0.008971099693083937</v>
+        <v>0.000589041678900246</v>
       </c>
       <c r="EN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP19" t="n">
-        <v>-0.03955339772846474</v>
+        <v>-0.002803627901362101</v>
       </c>
       <c r="EQ19" t="n">
         <v>0</v>
@@ -11116,16 +11116,16 @@
         <v>-0</v>
       </c>
       <c r="ES19" t="n">
-        <v>0.01707396175653479</v>
+        <v>-0.002360833967639047</v>
       </c>
       <c r="ET19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV19" t="n">
-        <v>-0.05177689511798572</v>
+        <v>0.001070557596419295</v>
       </c>
       <c r="EW19" t="n">
         <v>-0</v>
@@ -11134,7 +11134,7 @@
         <v>-0</v>
       </c>
       <c r="EY19" t="n">
-        <v>-0.07138285562202</v>
+        <v>-0.001937564619092961</v>
       </c>
       <c r="EZ19" t="n">
         <v>-0</v>
@@ -11143,52 +11143,52 @@
         <v>-0</v>
       </c>
       <c r="FB19" t="n">
-        <v>0.01191862123720126</v>
+        <v>0.0008349734557409154</v>
       </c>
       <c r="FC19" t="n">
         <v>-0</v>
       </c>
       <c r="FD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE19" t="n">
-        <v>0.004611602747758623</v>
+        <v>0.001654351452650392</v>
       </c>
       <c r="FF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG19" t="n">
         <v>-0</v>
       </c>
       <c r="FH19" t="n">
-        <v>-0.09966108905153441</v>
+        <v>0.001915675646749825</v>
       </c>
       <c r="FI19" t="n">
         <v>-0</v>
       </c>
       <c r="FJ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK19" t="n">
-        <v>-0.05171182852001045</v>
+        <v>0.005043608054125603</v>
       </c>
       <c r="FL19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN19" t="n">
-        <v>-0.03692063635058573</v>
+        <v>-0.004518745643906748</v>
       </c>
       <c r="FO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ19" t="n">
-        <v>-0.003272277245768659</v>
+        <v>-0.00221303720823005</v>
       </c>
       <c r="FR19" t="n">
         <v>-0</v>
@@ -11197,25 +11197,25 @@
         <v>-0</v>
       </c>
       <c r="FT19" t="n">
-        <v>0.0402187181855065</v>
+        <v>0.003337249329316889</v>
       </c>
       <c r="FU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW19" t="n">
-        <v>-0.1188576185446882</v>
+        <v>-0.0005564651791892614</v>
       </c>
       <c r="FX19" t="n">
         <v>-0</v>
       </c>
       <c r="FY19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ19" t="n">
-        <v>-0.1109163597642436</v>
+        <v>-0.003682776071882483</v>
       </c>
       <c r="GA19" t="n">
         <v>0</v>
@@ -11227,36 +11227,36 @@
         <v>0</v>
       </c>
       <c r="GD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE19" t="n">
         <v>-0</v>
       </c>
       <c r="GF19" t="n">
-        <v>-0.06661526230372479</v>
+        <v>-0.003069417574226486</v>
       </c>
       <c r="GG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B20" t="n">
-        <v>0.3784423977202138</v>
+        <v>0.2661471133634044</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.08499377064788281</v>
+        <v>-0.1042560989219634</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1359918517780057</v>
+        <v>-0.006968520300967149</v>
       </c>
       <c r="F20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>-0</v>
@@ -11265,52 +11265,52 @@
         <v>-0</v>
       </c>
       <c r="I20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2414550793481232</v>
+        <v>0.2486683496589685</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.09178023892661362</v>
+        <v>-0.1607121456461867</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1248262180632028</v>
+        <v>-0.03891895151760005</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.06851985759793888</v>
+        <v>0.03733330043087967</v>
       </c>
       <c r="U20" t="n">
         <v>-0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.01017270117656288</v>
+        <v>-0.04314936672090318</v>
       </c>
       <c r="W20" t="n">
-        <v>0.03872065485702504</v>
+        <v>-0.03381292987854235</v>
       </c>
       <c r="X20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
         <v>-0</v>
@@ -11322,46 +11322,46 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.05318458972965274</v>
+        <v>-0.004306691013536664</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.01119597801969909</v>
+        <v>-0.06679355624902665</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.01307158849532138</v>
+        <v>-0.0393849049763909</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH20" t="n">
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.001566718327243887</v>
+        <v>0.09613770069251647</v>
       </c>
       <c r="AM20" t="n">
         <v>-0</v>
       </c>
       <c r="AN20" t="n">
-        <v>-0.04765017572025804</v>
+        <v>-0.04032721581621097</v>
       </c>
       <c r="AO20" t="n">
-        <v>-0.07634674681179875</v>
+        <v>0.06103433198035022</v>
       </c>
       <c r="AP20" t="n">
         <v>0</v>
@@ -11370,79 +11370,79 @@
         <v>-0</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS20" t="n">
         <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.3124271907115264</v>
+        <v>0.2496328940274402</v>
       </c>
       <c r="AV20" t="n">
         <v>-0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.01657173334104016</v>
+        <v>-0.04546255219458817</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.02539568740241504</v>
+        <v>-0.06971545747146449</v>
       </c>
       <c r="AY20" t="n">
         <v>-0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
         <v>-0</v>
       </c>
       <c r="BC20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>0.01015977755297876</v>
+        <v>-0.0234274317164164</v>
       </c>
       <c r="BE20" t="n">
         <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>-0.06600355083346017</v>
+        <v>0.003209437776849516</v>
       </c>
       <c r="BG20" t="n">
-        <v>-0.1132131469597479</v>
+        <v>-0.05030927695165339</v>
       </c>
       <c r="BH20" t="n">
         <v>0</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK20" t="n">
         <v>0</v>
       </c>
       <c r="BL20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.08928575743792562</v>
+        <v>-0.005205498240211162</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.04503057325732124</v>
+        <v>-0.01242199282300789</v>
       </c>
       <c r="BP20" t="n">
-        <v>0.1297877056452698</v>
+        <v>0.03441762711360349</v>
       </c>
       <c r="BQ20" t="n">
         <v>-0</v>
@@ -11451,55 +11451,55 @@
         <v>0</v>
       </c>
       <c r="BS20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT20" t="n">
         <v>-0</v>
       </c>
       <c r="BU20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV20" t="n">
-        <v>0.1541732486363307</v>
+        <v>0.1531362501284056</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX20" t="n">
-        <v>0.02788158847148807</v>
+        <v>-0.06769615807693104</v>
       </c>
       <c r="BY20" t="n">
-        <v>0.009481982130491215</v>
+        <v>-0.02071810330213973</v>
       </c>
       <c r="BZ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA20" t="n">
         <v>-0</v>
       </c>
       <c r="CB20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE20" t="n">
-        <v>-0.07486169474544029</v>
+        <v>-0.08418658297046745</v>
       </c>
       <c r="CF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG20" t="n">
-        <v>0.002371710103985848</v>
+        <v>0.05538408869733454</v>
       </c>
       <c r="CH20" t="n">
-        <v>-0.002266028847490837</v>
+        <v>0.01262975098816327</v>
       </c>
       <c r="CI20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ20" t="n">
         <v>-0</v>
@@ -11508,22 +11508,22 @@
         <v>0</v>
       </c>
       <c r="CL20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM20" t="n">
         <v>0</v>
       </c>
       <c r="CN20" t="n">
-        <v>-0.005799587666139025</v>
+        <v>-0.09626171915565021</v>
       </c>
       <c r="CO20" t="n">
         <v>-0</v>
       </c>
       <c r="CP20" t="n">
-        <v>-0.06460821423659921</v>
+        <v>0.1016047204527777</v>
       </c>
       <c r="CQ20" t="n">
-        <v>-0.08885098653566489</v>
+        <v>0.08209864374059882</v>
       </c>
       <c r="CR20" t="n">
         <v>0</v>
@@ -11535,25 +11535,25 @@
         <v>-0</v>
       </c>
       <c r="CU20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV20" t="n">
         <v>-0</v>
       </c>
       <c r="CW20" t="n">
-        <v>-0.06168224578963825</v>
+        <v>-0.08378995907935313</v>
       </c>
       <c r="CX20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY20" t="n">
-        <v>0.01842317740563864</v>
+        <v>0.06058036537630335</v>
       </c>
       <c r="CZ20" t="n">
-        <v>-0.003553999204073033</v>
+        <v>0.004754850017113317</v>
       </c>
       <c r="DA20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB20" t="n">
         <v>0</v>
@@ -11568,46 +11568,46 @@
         <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>-0.03703464197157599</v>
+        <v>-0.06168229417088695</v>
       </c>
       <c r="DG20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH20" t="n">
-        <v>0.04500773910048444</v>
+        <v>-0.009391760545893177</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.03012137332579269</v>
+        <v>-0.005832548561347021</v>
       </c>
       <c r="DJ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL20" t="n">
         <v>0</v>
       </c>
       <c r="DM20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN20" t="n">
         <v>-0</v>
       </c>
       <c r="DO20" t="n">
-        <v>-0.02282115146299802</v>
+        <v>-0.06701030514444596</v>
       </c>
       <c r="DP20" t="n">
         <v>0</v>
       </c>
       <c r="DQ20" t="n">
-        <v>0.07074860141920068</v>
+        <v>0.001836064958761574</v>
       </c>
       <c r="DR20" t="n">
-        <v>-0.02584756902652983</v>
+        <v>0.007355758758950038</v>
       </c>
       <c r="DS20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT20" t="n">
         <v>-0</v>
@@ -11616,58 +11616,58 @@
         <v>-0</v>
       </c>
       <c r="DV20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX20" t="n">
-        <v>0.04070447738824914</v>
+        <v>0.08212040606980527</v>
       </c>
       <c r="DY20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ20" t="n">
-        <v>0.001506810728060333</v>
+        <v>0.0156813193214984</v>
       </c>
       <c r="EA20" t="n">
-        <v>-0.0532726921611872</v>
+        <v>-0.04094498799827561</v>
       </c>
       <c r="EB20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED20" t="n">
         <v>0</v>
       </c>
       <c r="EE20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF20" t="n">
         <v>0</v>
       </c>
       <c r="EG20" t="n">
-        <v>-0.06889006452956019</v>
+        <v>-0.07620186321609784</v>
       </c>
       <c r="EH20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI20" t="n">
-        <v>0.02938091262450172</v>
+        <v>0.06112881722188392</v>
       </c>
       <c r="EJ20" t="n">
-        <v>0.06840401566819709</v>
+        <v>0.0329064256139613</v>
       </c>
       <c r="EK20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN20" t="n">
         <v>-0</v>
@@ -11676,22 +11676,22 @@
         <v>0</v>
       </c>
       <c r="EP20" t="n">
-        <v>-0.04008013046892443</v>
+        <v>-0.01658880482272164</v>
       </c>
       <c r="EQ20" t="n">
         <v>0</v>
       </c>
       <c r="ER20" t="n">
-        <v>0.01549449635111666</v>
+        <v>0.04566983326285742</v>
       </c>
       <c r="ES20" t="n">
-        <v>0.01925860278712859</v>
+        <v>-0.006519249905984473</v>
       </c>
       <c r="ET20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV20" t="n">
         <v>0</v>
@@ -11700,19 +11700,19 @@
         <v>-0</v>
       </c>
       <c r="EX20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY20" t="n">
-        <v>-0.06074197038900458</v>
+        <v>-0.09005329532475757</v>
       </c>
       <c r="EZ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA20" t="n">
-        <v>0.008694033145647524</v>
+        <v>0.05735569452033878</v>
       </c>
       <c r="FB20" t="n">
-        <v>0.01318366956524479</v>
+        <v>0.004368558679191796</v>
       </c>
       <c r="FC20" t="n">
         <v>-0</v>
@@ -11724,22 +11724,22 @@
         <v>0</v>
       </c>
       <c r="FF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG20" t="n">
         <v>0</v>
       </c>
       <c r="FH20" t="n">
-        <v>0.005595449328151704</v>
+        <v>0.001666402443985255</v>
       </c>
       <c r="FI20" t="n">
         <v>-0</v>
       </c>
       <c r="FJ20" t="n">
-        <v>0.04261978380531131</v>
+        <v>0.04417491325432864</v>
       </c>
       <c r="FK20" t="n">
-        <v>-0.0618314720254417</v>
+        <v>-0.05618677526396558</v>
       </c>
       <c r="FL20" t="n">
         <v>-0</v>
@@ -11751,28 +11751,28 @@
         <v>-0</v>
       </c>
       <c r="FO20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ20" t="n">
-        <v>0.02270068528277099</v>
+        <v>-0.05864997385296194</v>
       </c>
       <c r="FR20" t="n">
         <v>-0</v>
       </c>
       <c r="FS20" t="n">
-        <v>0.02615062387732964</v>
+        <v>0.1072670231879525</v>
       </c>
       <c r="FT20" t="n">
-        <v>0.016360953550222</v>
+        <v>0.01197596863747839</v>
       </c>
       <c r="FU20" t="n">
         <v>-0</v>
       </c>
       <c r="FV20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW20" t="n">
         <v>0</v>
@@ -11781,28 +11781,28 @@
         <v>0</v>
       </c>
       <c r="FY20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ20" t="n">
-        <v>0.01033652071667932</v>
+        <v>-0.09338791888081929</v>
       </c>
       <c r="GA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB20" t="n">
-        <v>-0.03380742047934117</v>
+        <v>0.03977213896561099</v>
       </c>
       <c r="GC20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG20" t="n">
         <v>-0</v>
